--- a/jpcore-r4b/develop/StructureDefinition-jp-medicationadministration-injection.xlsx
+++ b/jpcore-r4b/develop/StructureDefinition-jp-medicationadministration-injection.xlsx
@@ -69,7 +69,7 @@
     <t>Contact</t>
   </si>
   <si>
-    <t>No display for ContactDetail</t>
+    <t>FHIR Japanese implementation research working group in Japan Association of Medical Informatics (JAMI) (http://jpfhir.jp, office@hlfhir.jp)</t>
   </si>
   <si>
     <t>Jurisdiction</t>

--- a/jpcore-r4b/develop/StructureDefinition-jp-medicationadministration-injection.xlsx
+++ b/jpcore-r4b/develop/StructureDefinition-jp-medicationadministration-injection.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3910" uniqueCount="633">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3910" uniqueCount="630">
   <si>
     <t>Property</t>
   </si>
@@ -1890,17 +1890,13 @@
     <t>1回の投与イベントで投与される薬剤の量。この値は、投与が錠剤の飲み込みや注射などの本質的に瞬間的なイベントである場合に使用する。</t>
   </si>
   <si>
-    <t>薬剤に関する簡易的な数量と単位を定めている。ValueおよびCodeを必須とし、comparatorは記述不可。単位についてはMERIT9医薬品単位略号の利用を推進している。(**SHOULD**)</t>
-  </si>
-  <si>
-    <t>ele-1:All FHIR elements must have a @value or children unless an empty Parameters resource {hasValue() or (children().count() &gt; id.count()) or $this is Parameters}
-qty-3:If a code for the unit is present, the system SHALL also be present {code.empty() or system.exists()}sqty-1:The comparator is not used on a SimpleQuantity {comparator.empty()}</t>
-  </si>
-  <si>
-    <t>PQ, IVL&lt;PQ&gt;, MO, CO, depending on the values</t>
-  </si>
-  <si>
-    <t>SN (see also Range) or CQ</t>
+    <t>If the administration is not instantaneous (rate is present), this can be specified to convey the total amount administered over period of time of a single administration.</t>
+  </si>
+  <si>
+    <t>.doseQuantity</t>
+  </si>
+  <si>
+    <t>RXA-6 Administered Amount / RXA-7 Administered Units</t>
   </si>
   <si>
     <t>MedicationAdministration.dosage.rate[x]</t>
@@ -1943,17 +1939,13 @@
 </t>
   </si>
   <si>
-    <t>単位時間内での薬剤の容量</t>
-  </si>
-  <si>
-    <t>The Ratio datatype should only be used to express a relationship of two numbers if the relationship cannot be suitably expressed using a Quantity and a common unit.  Where the denominator value is known to be fixed to "1", Quantity should be used instead of Ratio.</t>
-  </si>
-  <si>
-    <t>ele-1:All FHIR elements must have a @value or children unless an empty Parameters resource {hasValue() or (children().count() &gt; id.count()) or $this is Parameters}
-rat-1:Numerator and denominator SHALL both be present, or both are absent. If both are absent, there SHALL be some extension present {(numerator.exists() and denominator.exists()) or (numerator.empty() and denominator.empty() and extension.exists())}</t>
-  </si>
-  <si>
-    <t>RTO</t>
+    <t>Dose quantity per unit of time</t>
+  </si>
+  <si>
+    <t>Identifies the speed with which the medication was or will be introduced into the patient.  Typically, the rate for an infusion e.g. 100 ml per 1 hour or 100 ml/hr.  May also be expressed as a rate per unit of time, e.g. 500 ml per 2 hours.  Other examples:  200 mcg/min or 200 mcg/1 minute; 1 liter/8 hours.</t>
+  </si>
+  <si>
+    <t>If the rate changes over time, and you want to capture this in MedicationAdministration, then each change should be captured as a distinct MedicationAdministration, with a specific MedicationAdministration.dosage.rate, and the date time when the rate change occurred. Typically, the MedicationAdministration.dosage.rate element is not used to convey an average rate.</t>
   </si>
   <si>
     <t>MedicationAdministration.dosage.rate[x]:rateQuantity</t>
@@ -1967,9 +1959,6 @@
   </si>
   <si>
     <t>投与速度(流量)を指定する単位は流量を表す単位（e.g. 量/時間)を指定する</t>
-  </si>
-  <si>
-    <t>The context of use may frequently define what kind of quantity this is and therefore what kind of units can be used. The context of use may also restrict the values for the comparator.</t>
   </si>
   <si>
     <t>MedicationAdministration.eventHistory</t>
@@ -14105,22 +14094,22 @@
         <v>90</v>
       </c>
       <c r="AI101" t="s" s="2">
-        <v>148</v>
+        <v>79</v>
       </c>
       <c r="AJ101" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AK101" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AL101" t="s" s="2">
         <v>603</v>
       </c>
-      <c r="AK101" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AL101" t="s" s="2">
+      <c r="AM101" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AN101" t="s" s="2">
         <v>604</v>
-      </c>
-      <c r="AM101" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AN101" t="s" s="2">
-        <v>605</v>
       </c>
       <c r="AO101" t="s" s="2">
         <v>79</v>
@@ -14128,10 +14117,10 @@
     </row>
     <row r="102">
       <c r="A102" t="s" s="2">
-        <v>606</v>
+        <v>605</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>606</v>
+        <v>605</v>
       </c>
       <c r="C102" s="2"/>
       <c r="D102" t="s" s="2">
@@ -14154,16 +14143,16 @@
         <v>79</v>
       </c>
       <c r="K102" t="s" s="2">
+        <v>606</v>
+      </c>
+      <c r="L102" t="s" s="2">
         <v>607</v>
       </c>
-      <c r="L102" t="s" s="2">
+      <c r="M102" t="s" s="2">
         <v>608</v>
       </c>
-      <c r="M102" t="s" s="2">
+      <c r="N102" t="s" s="2">
         <v>609</v>
-      </c>
-      <c r="N102" t="s" s="2">
-        <v>610</v>
       </c>
       <c r="O102" s="2"/>
       <c r="P102" t="s" s="2">
@@ -14201,17 +14190,17 @@
         <v>79</v>
       </c>
       <c r="AB102" t="s" s="2">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="AC102" s="2"/>
       <c r="AD102" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AE102" t="s" s="2">
-        <v>612</v>
+        <v>611</v>
       </c>
       <c r="AF102" t="s" s="2">
-        <v>606</v>
+        <v>605</v>
       </c>
       <c r="AG102" t="s" s="2">
         <v>80</v>
@@ -14229,13 +14218,13 @@
         <v>79</v>
       </c>
       <c r="AL102" t="s" s="2">
+        <v>612</v>
+      </c>
+      <c r="AM102" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AN102" t="s" s="2">
         <v>613</v>
-      </c>
-      <c r="AM102" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AN102" t="s" s="2">
-        <v>614</v>
       </c>
       <c r="AO102" t="s" s="2">
         <v>79</v>
@@ -14243,13 +14232,13 @@
     </row>
     <row r="103">
       <c r="A103" t="s" s="2">
+        <v>614</v>
+      </c>
+      <c r="B103" t="s" s="2">
+        <v>605</v>
+      </c>
+      <c r="C103" t="s" s="2">
         <v>615</v>
-      </c>
-      <c r="B103" t="s" s="2">
-        <v>606</v>
-      </c>
-      <c r="C103" t="s" s="2">
-        <v>616</v>
       </c>
       <c r="D103" t="s" s="2">
         <v>79</v>
@@ -14271,10 +14260,10 @@
         <v>79</v>
       </c>
       <c r="K103" t="s" s="2">
+        <v>616</v>
+      </c>
+      <c r="L103" t="s" s="2">
         <v>617</v>
-      </c>
-      <c r="L103" t="s" s="2">
-        <v>618</v>
       </c>
       <c r="M103" t="s" s="2">
         <v>618</v>
@@ -14330,7 +14319,7 @@
         <v>79</v>
       </c>
       <c r="AF103" t="s" s="2">
-        <v>606</v>
+        <v>605</v>
       </c>
       <c r="AG103" t="s" s="2">
         <v>80</v>
@@ -14339,22 +14328,22 @@
         <v>90</v>
       </c>
       <c r="AI103" t="s" s="2">
-        <v>148</v>
+        <v>79</v>
       </c>
       <c r="AJ103" t="s" s="2">
-        <v>620</v>
+        <v>102</v>
       </c>
       <c r="AK103" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AL103" t="s" s="2">
-        <v>621</v>
+        <v>612</v>
       </c>
       <c r="AM103" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AN103" t="s" s="2">
-        <v>134</v>
+        <v>613</v>
       </c>
       <c r="AO103" t="s" s="2">
         <v>79</v>
@@ -14362,13 +14351,13 @@
     </row>
     <row r="104">
       <c r="A104" t="s" s="2">
-        <v>622</v>
+        <v>620</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>606</v>
+        <v>605</v>
       </c>
       <c r="C104" t="s" s="2">
-        <v>623</v>
+        <v>621</v>
       </c>
       <c r="D104" t="s" s="2">
         <v>79</v>
@@ -14390,16 +14379,16 @@
         <v>79</v>
       </c>
       <c r="K104" t="s" s="2">
-        <v>624</v>
+        <v>622</v>
       </c>
       <c r="L104" t="s" s="2">
-        <v>625</v>
+        <v>623</v>
       </c>
       <c r="M104" t="s" s="2">
-        <v>625</v>
+        <v>623</v>
       </c>
       <c r="N104" t="s" s="2">
-        <v>626</v>
+        <v>619</v>
       </c>
       <c r="O104" s="2"/>
       <c r="P104" t="s" s="2">
@@ -14449,7 +14438,7 @@
         <v>79</v>
       </c>
       <c r="AF104" t="s" s="2">
-        <v>606</v>
+        <v>605</v>
       </c>
       <c r="AG104" t="s" s="2">
         <v>80</v>
@@ -14458,22 +14447,22 @@
         <v>90</v>
       </c>
       <c r="AI104" t="s" s="2">
-        <v>148</v>
+        <v>79</v>
       </c>
       <c r="AJ104" t="s" s="2">
-        <v>603</v>
+        <v>102</v>
       </c>
       <c r="AK104" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AL104" t="s" s="2">
-        <v>604</v>
+        <v>612</v>
       </c>
       <c r="AM104" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AN104" t="s" s="2">
-        <v>605</v>
+        <v>613</v>
       </c>
       <c r="AO104" t="s" s="2">
         <v>79</v>
@@ -14481,10 +14470,10 @@
     </row>
     <row r="105">
       <c r="A105" t="s" s="2">
-        <v>627</v>
+        <v>624</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>627</v>
+        <v>624</v>
       </c>
       <c r="C105" s="2"/>
       <c r="D105" t="s" s="2">
@@ -14507,16 +14496,16 @@
         <v>79</v>
       </c>
       <c r="K105" t="s" s="2">
+        <v>625</v>
+      </c>
+      <c r="L105" t="s" s="2">
+        <v>626</v>
+      </c>
+      <c r="M105" t="s" s="2">
+        <v>627</v>
+      </c>
+      <c r="N105" t="s" s="2">
         <v>628</v>
-      </c>
-      <c r="L105" t="s" s="2">
-        <v>629</v>
-      </c>
-      <c r="M105" t="s" s="2">
-        <v>630</v>
-      </c>
-      <c r="N105" t="s" s="2">
-        <v>631</v>
       </c>
       <c r="O105" s="2"/>
       <c r="P105" t="s" s="2">
@@ -14566,7 +14555,7 @@
         <v>79</v>
       </c>
       <c r="AF105" t="s" s="2">
-        <v>627</v>
+        <v>624</v>
       </c>
       <c r="AG105" t="s" s="2">
         <v>80</v>
@@ -14584,7 +14573,7 @@
         <v>79</v>
       </c>
       <c r="AL105" t="s" s="2">
-        <v>632</v>
+        <v>629</v>
       </c>
       <c r="AM105" t="s" s="2">
         <v>79</v>

--- a/jpcore-r4b/develop/StructureDefinition-jp-medicationadministration-injection.xlsx
+++ b/jpcore-r4b/develop/StructureDefinition-jp-medicationadministration-injection.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2.0.0-dev</t>
+    <t>2.0.0-dev-temp</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-10-31</t>
+    <t>2025-07-30</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -90,7 +90,7 @@
     <t>Copyright</t>
   </si>
   <si>
-    <t>Copyright FHIR Japanese implementation research working group in Japan Association of Medical Informatics (JAMI) 一般社団法人日本医療情報学会NeXEHRS課題研究会FHIR日本実装検討WG</t>
+    <t>Copyright Japan FHIR Implementation Infrastructure Study Group in Japan Association of Medical Informatics (JAMI) 一般社団法人日本医療情報学会FHIR国内実装基盤研究会</t>
   </si>
   <si>
     <t>FHIR Version</t>
@@ -370,7 +370,7 @@
     <t>IETF language tag</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/languages</t>
+    <t>http://hl7.org/fhir/ValueSet/languages|4.3.0</t>
   </si>
   <si>
     <t>Resource.language</t>
@@ -709,7 +709,7 @@
     <t>extensible</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/identifier-type</t>
+    <t>http://hl7.org/fhir/ValueSet/identifier-type|4.3.0</t>
   </si>
   <si>
     <t>Identifier.type</t>
@@ -727,7 +727,7 @@
     <t>Rp番号(剤グループ番号)についてのsystem値</t>
   </si>
   <si>
-    <t>ここで付番されたIDがRp番号であることを明示するためにOIDとして定義された。urn:oid:1.2.392.100495.20.3.81で固定される。</t>
+    <t>ここで付番されたIDがRp番号であることを明示するためにOID-urlとして定義された。http://jpfhir.jp/fhir/core/mhlw/IdSystem/Medication-RPGroupNumberで固定される。</t>
   </si>
   <si>
     <t>Identifier.system is always case sensitive.</t>
@@ -736,7 +736,7 @@
     <t>There are many sets  of identifiers.  To perform matching of two identifiers, we need to know what set we're dealing with. The system identifies a particular set of unique identifiers.</t>
   </si>
   <si>
-    <t>urn:oid:1.2.392.100495.20.3.81</t>
+    <t>http://jpfhir.jp/fhir/core/mhlw/IdSystem/Medication-RPGroupNumber</t>
   </si>
   <si>
     <t>http://www.acme.com/identifiers/patient</t>
@@ -813,7 +813,7 @@
     <t>MedicationAdministration.identifier.assigner</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Organization)
+    <t xml:space="preserve">Reference(Organization|4.3.0)
 </t>
   </si>
   <si>
@@ -871,7 +871,7 @@
     <t>Establishes the namespace for the value - that is, a URL that describes a set values that are unique.</t>
   </si>
   <si>
-    <t>http://jpfhir.jp/fhir/core/IdSystem/resourceInstance-identifier</t>
+    <t>urn:oid:1.2.392.100495.20.3.11</t>
   </si>
   <si>
     <t>MedicationAdministration.identifier:requestIdentifier.value</t>
@@ -910,7 +910,7 @@
     <t>MedicationAdministration.partOf</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(MedicationAdministration|Procedure)
+    <t xml:space="preserve">Reference(MedicationAdministration|4.3.0|Procedure|4.3.0)
 </t>
   </si>
   <si>
@@ -972,7 +972,7 @@
     <t>A set of codes indicating the reason why the MedicationAdministration is negated.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/reason-medication-not-given-codes</t>
+    <t>http://hl7.org/fhir/ValueSet/reason-medication-not-given-codes|4.3.0</t>
   </si>
   <si>
     <t>Event.statusReason</t>
@@ -996,7 +996,7 @@
     <t>A coded concept describing where the medication administered is expected to occur.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/medication-admin-category</t>
+    <t>http://hl7.org/fhir/ValueSet/medication-admin-category|4.3.0</t>
   </si>
   <si>
     <t>.inboundRelationship[typeCode=COMP].source[classCode=OBS, moodCode=EVN, code="type of medication usage"].value</t>
@@ -1012,7 +1012,7 @@
     <t>医薬品</t>
   </si>
   <si>
-    <t>投与された薬剤を識別する。既知の薬のリストから薬を識別するコード情報を設定する。</t>
+    <t>医薬品の識別情報は必須でありmedicationReference.referenceが必ず存在しなければならない、JP Coreでは注射の医薬品情報は単一薬剤の場合も Medicationリソースとして記述し、medicationCodeableConceptは使用しない。参照するMedicationリソースは、MedicationRequest.contained属性に内包することが望ましいが、外部参照としても良い。</t>
   </si>
   <si>
     <t>ひとつのtext要素と、複数のcoding 要素を記述できる。処方オーダ時に選択または入力し、実際に処方箋に印字される文字列を必ずtext要素に格納した上で、それをコード化した情報を1個以上のcoding 要素に記述する。  
@@ -1038,7 +1038,7 @@
     <t>MedicationAdministration.subject</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Patient|Group)
+    <t xml:space="preserve">Reference(Patient|4.3.0|Group|4.3.0)
 </t>
   </si>
   <si>
@@ -1063,7 +1063,7 @@
     <t>MedicationAdministration.context</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Encounter|EpisodeOfCare)
+    <t xml:space="preserve">Reference(Encounter|4.3.0|EpisodeOfCare|4.3.0)
 </t>
   </si>
   <si>
@@ -1088,7 +1088,7 @@
     <t>MedicationAdministration.supportingInformation</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Resource)
+    <t xml:space="preserve">Reference(Resource|4.3.0)
 </t>
   </si>
   <si>
@@ -1190,7 +1190,7 @@
     <t>A code describing the role an individual played in administering the medication.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/med-admin-perform-function</t>
+    <t>http://hl7.org/fhir/ValueSet/med-admin-perform-function|4.3.0</t>
   </si>
   <si>
     <t>Event.performer.function</t>
@@ -1202,7 +1202,7 @@
     <t>MedicationAdministration.performer.actor</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Practitioner|PractitionerRole|Patient|RelatedPerson|Device)
+    <t xml:space="preserve">Reference(Practitioner|4.3.0|PractitionerRole|4.3.0|Patient|4.3.0|RelatedPerson|4.3.0|Device|4.3.0)
 </t>
   </si>
   <si>
@@ -1230,7 +1230,7 @@
     <t>A set of codes indicating the reason why the MedicationAdministration was made.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/reason-medication-given-codes</t>
+    <t>http://hl7.org/fhir/ValueSet/reason-medication-given-codes|4.3.0</t>
   </si>
   <si>
     <t>Event.reasonCode</t>
@@ -1245,7 +1245,7 @@
     <t>MedicationAdministration.reasonReference</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Condition|Observation|DiagnosticReport)
+    <t xml:space="preserve">Reference(Condition|4.3.0|Observation|4.3.0|DiagnosticReport|4.3.0)
 </t>
   </si>
   <si>
@@ -1273,7 +1273,7 @@
     <t>MedicationAdministration.request</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(MedicationRequest)
+    <t xml:space="preserve">Reference(MedicationRequest|4.3.0)
 </t>
   </si>
   <si>
@@ -1298,7 +1298,7 @@
     <t>MedicationAdministration.device</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Device)
+    <t xml:space="preserve">Reference(Device|4.3.0)
 </t>
   </si>
   <si>
@@ -1484,7 +1484,7 @@
     <t>bodySite</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {bodySite}
+    <t xml:space="preserve">Extension {bodySite|5.2.0}
 </t>
   </si>
   <si>
@@ -1623,7 +1623,7 @@
     <t>A coded concept describing the technique by which the medicine is administered.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/administration-method-codes</t>
+    <t>http://hl7.org/fhir/ValueSet/administration-method-codes|4.3.0</t>
   </si>
   <si>
     <t>.methodCode</t>
@@ -1708,7 +1708,7 @@
     <t>Need to be unambiguous about the source of the definition of the symbol.</t>
   </si>
   <si>
-    <t>urn:oid:1.2.392.200250.2.2.20.30</t>
+    <t>http://jami.jp/CodeSystem/MedicationMethodBasicUsage</t>
   </si>
   <si>
     <t>Coding.system</t>
@@ -1832,7 +1832,7 @@
     <t>投与⽅法に対応するJAMI 用法コード表基本用法2桁コード</t>
   </si>
   <si>
-    <t>投与⽅法に対応するJAMI 用法コード表基本用法2桁コードを識別するURI。２桁コードurn:oid:1.2.392.200250.2.2.20.40</t>
+    <t>投与⽅法に対応するJAMI 用法コード表基本用法2桁コードを識別するURI。２桁コードhttp://jami.jp/CodeSystem/MedicationUsage</t>
   </si>
   <si>
     <t>http://jpfhir.jp/fhir/core/ValueSet/JP_MedicationMethodJAMIDetailUsage_VS</t>
@@ -1847,7 +1847,7 @@
     <t>MedicationAdministration.dosage.method.coding:unitDigit2.system</t>
   </si>
   <si>
-    <t>urn:oid:1.2.392.200250.2.2.20.40</t>
+    <t>http://jami.jp/CodeSystem/MedicationMethodDetailUsage</t>
   </si>
   <si>
     <t>MedicationAdministration.dosage.method.coding:unitDigit2.version</t>
@@ -1903,7 +1903,7 @@
   </si>
   <si>
     <t>Ratio
-Quantity {SimpleQuantity}</t>
+Quantity {SimpleQuantity|4.3.0}</t>
   </si>
   <si>
     <t>単位時間あたりの用量</t>
@@ -1964,7 +1964,7 @@
     <t>MedicationAdministration.eventHistory</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Provenance)
+    <t xml:space="preserve">Reference(Provenance|4.3.0)
 </t>
   </si>
   <si>
@@ -2284,17 +2284,17 @@
   <dimension ref="A1:AO105"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="68.30859375" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="58.66015625" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="23.1328125" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="4" max="4" width="39.9140625" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="5" max="5" width="6.77734375" customWidth="true" bestFit="true"/>
-    <col min="6" max="6" width="4.9453125" customWidth="true" bestFit="true"/>
-    <col min="7" max="7" width="5.4296875" customWidth="true" bestFit="true"/>
-    <col min="8" max="8" width="16.27734375" customWidth="true" bestFit="true"/>
-    <col min="9" max="9" width="13.26171875" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="58.5625" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="50.2890625" customWidth="true" bestFit="true"/>
+    <col min="3" max="3" width="19.83203125" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="4" max="4" width="34.21875" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="5" max="5" width="5.80859375" customWidth="true" bestFit="true"/>
+    <col min="6" max="6" width="4.23828125" customWidth="true" bestFit="true"/>
+    <col min="7" max="7" width="4.65625" customWidth="true" bestFit="true"/>
+    <col min="8" max="8" width="13.953125" customWidth="true" bestFit="true"/>
+    <col min="9" max="9" width="11.3671875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="111.4140625" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="95.515625" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
@@ -2303,27 +2303,27 @@
     <col min="17" max="17" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="18" max="18" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="19" max="19" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="20" max="20" width="38.2265625" customWidth="true" bestFit="true"/>
-    <col min="21" max="21" width="17.171875" customWidth="true" bestFit="true"/>
-    <col min="22" max="22" width="17.65625" customWidth="true" bestFit="true"/>
-    <col min="23" max="23" width="19.03515625" customWidth="true" bestFit="true"/>
-    <col min="24" max="24" width="18.859375" customWidth="true" bestFit="true"/>
-    <col min="25" max="25" width="79.59375" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="69.23046875" customWidth="true" bestFit="true"/>
-    <col min="27" max="27" width="6.34765625" customWidth="true" bestFit="true"/>
-    <col min="28" max="28" width="22.71875" customWidth="true" bestFit="true"/>
-    <col min="29" max="29" width="42.03515625" customWidth="true" bestFit="true"/>
-    <col min="30" max="30" width="17.21484375" customWidth="true" bestFit="true"/>
-    <col min="31" max="31" width="14.4140625" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="32" max="32" width="45.6171875" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="33" max="33" width="10.5546875" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="34" max="34" width="11.0390625" customWidth="true" bestFit="true"/>
+    <col min="20" max="20" width="32.7734375" customWidth="true" bestFit="true"/>
+    <col min="21" max="21" width="14.72265625" customWidth="true" bestFit="true"/>
+    <col min="22" max="22" width="15.13671875" customWidth="true" bestFit="true"/>
+    <col min="23" max="23" width="16.3203125" customWidth="true" bestFit="true"/>
+    <col min="24" max="24" width="16.16796875" customWidth="true" bestFit="true"/>
+    <col min="25" max="25" width="68.23828125" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="59.3515625" customWidth="true" bestFit="true"/>
+    <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
+    <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
+    <col min="29" max="29" width="36.0390625" customWidth="true" bestFit="true"/>
+    <col min="30" max="30" width="14.7578125" customWidth="true" bestFit="true"/>
+    <col min="31" max="31" width="12.359375" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="32" max="32" width="39.109375" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="33" max="33" width="9.046875" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="34" max="34" width="9.46484375" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
-    <col min="37" max="37" width="29.69921875" customWidth="true" bestFit="true"/>
-    <col min="38" max="38" width="255.0" customWidth="true" bestFit="true"/>
-    <col min="39" max="39" width="36.91796875" customWidth="true" bestFit="true"/>
-    <col min="40" max="40" width="101.08984375" customWidth="true" bestFit="true"/>
-    <col min="41" max="41" width="22.50390625" customWidth="true" bestFit="true"/>
+    <col min="37" max="37" width="25.4609375" customWidth="true" bestFit="true"/>
+    <col min="38" max="38" width="245.42578125" customWidth="true" bestFit="true"/>
+    <col min="39" max="39" width="31.65234375" customWidth="true" bestFit="true"/>
+    <col min="40" max="40" width="86.66796875" customWidth="true" bestFit="true"/>
+    <col min="41" max="41" width="19.29296875" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -10260,7 +10260,7 @@
         <v>80</v>
       </c>
       <c r="G69" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="H69" t="s" s="2">
         <v>79</v>

--- a/jpcore-r4b/develop/StructureDefinition-jp-medicationadministration-injection.xlsx
+++ b/jpcore-r4b/develop/StructureDefinition-jp-medicationadministration-injection.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2.0.0-dev-temp</t>
+    <t>2.0.0-dev</t>
   </si>
   <si>
     <t>Name</t>

--- a/jpcore-r4b/develop/StructureDefinition-jp-medicationadministration-injection.xlsx
+++ b/jpcore-r4b/develop/StructureDefinition-jp-medicationadministration-injection.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3910" uniqueCount="630">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3910" uniqueCount="637">
   <si>
     <t>Property</t>
   </si>
@@ -268,11 +268,11 @@
     <t>患者への注射薬剤投与記録</t>
   </si>
   <si>
-    <t>Describes the event of a patient consuming or otherwise being administered a medication.  This may be as simple as swallowing a tablet or it may be a long running infusion.  Related resources tie this event to the authorizing prescription, and the specific encounter between patient and health care practitioner.</t>
-  </si>
-  <si>
-    <t>dom-2:If the resource is contained in another resource, it SHALL NOT contain nested Resources {contained.contained.empty()}
-dom-3:If the resource is contained in another resource, it SHALL be referred to from elsewhere in the resource or SHALL refer to the containing resource {contained.where(((id.exists() and ('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url)))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(uri) = '#').exists()).not()).trace('unmatched', id).empty()}dom-4:If a resource is contained in another resource, it SHALL NOT have a meta.versionId or a meta.lastUpdated {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-5:If a resource is contained in another resource, it SHALL NOT have a security label {contained.meta.security.empty()}dom-6:A resource should have narrative for robust management {text.`div`.exists()}</t>
+    <t>患者が薬剤を服用する、あるいは投与される事象を説明します。これは、錠剤を飲むだけだったり、長時間の点滴だったりすることがあります。関連するリソースは、この事象を許可された処方箋や、患者と医療従事者の具体的な受療行動と結びつけます。 / Describes the event of a patient consuming or otherwise being administered a medication.  This may be as simple as swallowing a tablet or it may be a long running infusion.  Related resources tie this event to the authorizing prescription, and the specific encounter between patient and health care practitioner.</t>
+  </si>
+  <si>
+    <t>dom-2:もしリソースが他のリソースに含まれている場合、そのリソースにはネストされたリソースを含めてはなりません (moshi risōsu ga hoka no risōsu ni fukumarete iru baai, sono risōsu ni wa nesuto sareta risōsu o fukumete wa narimasen). / If the resource is contained in another resource, it SHALL NOT contain nested Resources {contained.contained.empty()}
+dom-3:もしリソースが他のリソースに含まれている場合、それはリソースの他の場所から参照されるか、含まれるリソースに参照されるべきです。 / If the resource is contained in another resource, it SHALL be referred to from elsewhere in the resource or SHALL refer to the containing resource {contained.where(((id.exists() and ('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url)))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(uri) = '#').exists()).not()).trace('unmatched', id).empty()}dom-4:もしリソースが別のリソースの中に含まれる場合、meta.versionIdまたはmeta.lastUpdatedを持つべきではありません。 / If a resource is contained in another resource, it SHALL NOT have a meta.versionId or a meta.lastUpdated {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-5:もしリソースが他のリソースに含まれている場合、セキュリティラベルを持つべきではありません。 / If a resource is contained in another resource, it SHALL NOT have a security label {contained.meta.security.empty()}dom-6:資源は堅牢な管理のために物語を持つべきである。 / A resource should have narrative for robust management {text.`div`.exists()}</t>
   </si>
   <si>
     <t>Event</t>
@@ -297,13 +297,13 @@
 </t>
   </si>
   <si>
-    <t>Logical id of this artifact</t>
-  </si>
-  <si>
-    <t>The logical id of the resource, as used in the URL for the resource. Once assigned, this value never changes.</t>
-  </si>
-  <si>
-    <t>The only time that a resource does not have an id is when it is being submitted to the server using a create operation.</t>
+    <t>このアーティファクトの論理ID / Logical id of this artifact</t>
+  </si>
+  <si>
+    <t>リソースのURLで使用される論理ID。一度割り当てられたら、この値は変更されません。 / The logical id of the resource, as used in the URL for the resource. Once assigned, this value never changes.</t>
+  </si>
+  <si>
+    <t>リソースにIDがないのは、作成操作を使用してサーバーに送信されているときだけです。 / The only time that a resource does not have an id is when it is being submitted to the server using a create operation.</t>
   </si>
   <si>
     <t>Resource.id</t>
@@ -316,16 +316,16 @@
 </t>
   </si>
   <si>
-    <t>Metadata about the resource</t>
-  </si>
-  <si>
-    <t>The metadata about the resource. This is content that is maintained by the infrastructure. Changes to the content might not always be associated with version changes to the resource.</t>
+    <t>リソースに関するMetadata / Metadata about the resource</t>
+  </si>
+  <si>
+    <t>リソースに関するMetadata。これはインフラストラクチャによって維持されるコンテンツです。 コンテンツの変更は、リソースのバージョン変更と常に関連しているわけではありません。 / The metadata about the resource. This is content that is maintained by the infrastructure. Changes to the content might not always be associated with version changes to the resource.</t>
   </si>
   <si>
     <t>Resource.meta</t>
   </si>
   <si>
-    <t xml:space="preserve">ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+    <t xml:space="preserve">ele-1:すべてのFHIR要素は、@valueまたはchildrenを持っている必要があります。 / All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
 </t>
   </si>
   <si>
@@ -336,13 +336,13 @@
 </t>
   </si>
   <si>
-    <t>A set of rules under which this content was created</t>
-  </si>
-  <si>
-    <t>A reference to a set of rules that were followed when the resource was constructed, and which must be understood when processing the content. Often, this is a reference to an implementation guide that defines the special rules along with other profiles etc.</t>
-  </si>
-  <si>
-    <t>Asserting this rule set restricts the content to be only understood by a limited set of trading partners. This inherently limits the usefulness of the data in the long term. However, the existing health eco-system is highly fractured, and not yet ready to define, collect, and exchange data in a generally computable sense. Wherever possible, implementers and/or specification writers should avoid using this element. Often, when used, the URL is a reference to an implementation guide that defines these special rules as part of it's narrative along with other profiles, value sets, etc.</t>
+    <t>このコンテンツが作成されたルールセット / A set of rules under which this content was created</t>
+  </si>
+  <si>
+    <t>リソース構築時に遵守された一連のルールを指すものであり、コンテンツを処理する際に理解する必要があります。しばしば、特別なルールを定義する実装ガイドとその他のプロファイルなどを含むものです。 / A reference to a set of rules that were followed when the resource was constructed, and which must be understood when processing the content. Often, this is a reference to an implementation guide that defines the special rules along with other profiles etc.</t>
+  </si>
+  <si>
+    <t>このルールセットを主張することで、取引先の限られた集団にしか内容を理解させることができず、長期的にはデータの有用性が制限されます。しかしながら、現存するヘルスエコシステムは高度に分断化しており、一般的に計算可能な形式でデータを定義、収集、交換する準備が整っていません。できる限り、実装者および/または仕様ライターはこの要素の使用を避けるべきです。使用する場合、URLは、そのナラティブとともに他のプロファイル、値セットなどを含む実装ガイドを定義する参照となります。 / Asserting this rule set restricts the content to be only understood by a limited set of trading partners. This inherently limits the usefulness of the data in the long term. However, the existing health eco-system is highly fractured, and not yet ready to define, collect, and exchange data in a generally computable sense. Wherever possible, implementers and/or specification writers should avoid using this element. Often, when used, the URL is a reference to an implementation guide that defines these special rules as part of it's narrative along with other profiles, value sets, etc.</t>
   </si>
   <si>
     <t>Resource.implicitRules</t>
@@ -355,19 +355,19 @@
 </t>
   </si>
   <si>
-    <t>Language of the resource content</t>
-  </si>
-  <si>
-    <t>The base language in which the resource is written.</t>
-  </si>
-  <si>
-    <t>Language is provided to support indexing and accessibility (typically, services such as text to speech use the language tag). The html language tag in the narrative applies  to the narrative. The language tag on the resource may be used to specify the language of other presentations generated from the data in the resource. Not all the content has to be in the base language. The Resource.language should not be assumed to apply to the narrative automatically. If a language is specified, it should it also be specified on the div element in the html (see rules in HTML5 for information about the relationship between xml:lang and the html lang attribute).</t>
+    <t>リソースコンテンツの言語 / Language of the resource content</t>
+  </si>
+  <si>
+    <t>リソースが書かれている基本言語。 / The base language in which the resource is written.</t>
+  </si>
+  <si>
+    <t>言語はインデックスとアクセシビリティをサポートするために提供されます（通常、テキスト読み上げなどのサービスは言語タグを使用します）。物語のHTML言語タグは、物語に適用されます。リソース上の言語タグは、リソース内のデータから生成される他のプレゼンテーションの言語を指定するために使用できます。すべてのコンテンツが基本言語である必要はありません。Resource.languageは自動的に物語に適用されたと想定してはいけません。言語が指定されている場合、HTMLのdiv要素にも指定する必要があります（xml：langとhtml lang属性の関係に関する情報はHTML5の規則を参照）。 / Language is provided to support indexing and accessibility (typically, services such as text to speech use the language tag). The html language tag in the narrative applies  to the narrative. The language tag on the resource may be used to specify the language of other presentations generated from the data in the resource. Not all the content has to be in the base language. The Resource.language should not be assumed to apply to the narrative automatically. If a language is specified, it should it also be specified on the div element in the html (see rules in HTML5 for information about the relationship between xml:lang and the html lang attribute).</t>
   </si>
   <si>
     <t>preferred</t>
   </si>
   <si>
-    <t>IETF language tag</t>
+    <t>人間の言語。 / IETF language tag</t>
   </si>
   <si>
     <t>http://hl7.org/fhir/ValueSet/languages|4.3.0</t>
@@ -387,13 +387,13 @@
 </t>
   </si>
   <si>
-    <t>Text summary of the resource, for human interpretation</t>
-  </si>
-  <si>
-    <t>A human-readable narrative that contains a summary of the resource and can be used to represent the content of the resource to a human. The narrative need not encode all the structured data, but is required to contain sufficient detail to make it "clinically safe" for a human to just read the narrative. Resource definitions may define what content should be represented in the narrative to ensure clinical safety.</t>
-  </si>
-  <si>
-    <t>Contained resources do not have narrative. Resources that are not contained SHOULD have a narrative. In some cases, a resource may only have text with little or no additional discrete data (as long as all minOccurs=1 elements are satisfied).  This may be necessary for data from legacy systems where information is captured as a "text blob" or where text is additionally entered raw or narrated and encoded information is added later.</t>
+    <t>人間の解釈のためのリソースのテキスト要約 / Text summary of the resource, for human interpretation</t>
+  </si>
+  <si>
+    <t>リソースの要約を含む人が読めるナビゲーションであり、リソースの内容を人に表現するために使用できます。ナビゲーションはすべての構造化されたデータをエンコードする必要はありませんが、人間がナビゲーションを読むだけで「臨床的に安全」であるために十分な詳細を含む必要があります。リソース定義には、臨床的な安全性を確保するためにナビゲーションで表現する必要があるコンテンツが定義される場合があります。 / A human-readable narrative that contains a summary of the resource and can be used to represent the content of the resource to a human. The narrative need not encode all the structured data, but is required to contain sufficient detail to make it "clinically safe" for a human to just read the narrative. Resource definitions may define what content should be represented in the narrative to ensure clinical safety.</t>
+  </si>
+  <si>
+    <t>含まれるリソースには説明がありません。含まれないリソースには説明が必要です。場合によっては、リソースが少量のデータしか含まず、テキストだけで表現されることがあります（minOccurs = 1要素がすべて満たされている限り）。これは、情報が「テキストの塊」としてキャプチャされるレガシーシステムからのデータや、テキストが生またはナレーションされて符号化された情報が後で追加される場合に必要な場合があります。 / Contained resources do not have narrative. Resources that are not contained SHOULD have a narrative. In some cases, a resource may only have text with little or no additional discrete data (as long as all minOccurs=1 elements are satisfied).  This may be necessary for data from legacy systems where information is captured as a "text blob" or where text is additionally entered raw or narrated and encoded information is added later.</t>
   </si>
   <si>
     <t>DomainResource.text</t>
@@ -413,19 +413,19 @@
 </t>
   </si>
   <si>
-    <t>Contained, inline Resources</t>
-  </si>
-  <si>
-    <t>These resources do not have an independent existence apart from the resource that contains them - they cannot be identified independently, and nor can they have their own independent transaction scope.</t>
-  </si>
-  <si>
-    <t>This should never be done when the content can be identified properly, as once identification is lost, it is extremely difficult (and context dependent) to restore it again. Contained resources may have profiles and tags In their meta elements, but SHALL NOT have security labels.</t>
+    <t>含まれている、インラインのリソース / Contained, inline Resources</t>
+  </si>
+  <si>
+    <t>これらのリソースは、それらを含むリソースから独立した存在を持ちません。それらは独立して識別することはできず、独自の独立したトランザクション範囲を持つこともできません。 / These resources do not have an independent existence apart from the resource that contains them - they cannot be identified independently, and nor can they have their own independent transaction scope.</t>
+  </si>
+  <si>
+    <t>コンテンツが適切に識別できる場合には、これを行うべきではありません。識別が失われると、再び復元することは非常に困難であり（文脈に依存します）、メタ要素にプロファイルとタグを持つことができますが、セキュリティのラベルを持っていてはいけません。 / This should never be done when the content can be identified properly, as once identification is lost, it is extremely difficult (and context dependent) to restore it again. Contained resources may have profiles and tags In their meta elements, but SHALL NOT have security labels.</t>
   </si>
   <si>
     <t>DomainResource.contained</t>
   </si>
   <si>
-    <t xml:space="preserve">dom-r4b:Containing new R4B resources within R4 resources may cause interoperability issues if instances are shared with R4 systems {($this is Citation or $this is Evidence or $this is EvidenceReport or $this is EvidenceVariable or $this is MedicinalProductDefinition or $this is PackagedProductDefinition or $this is AdministrableProductDefinition or $this is Ingredient or $this is ClinicalUseDefinition or $this is RegulatedAuthorization or $this is SubstanceDefinition or $this is SubscriptionStatus or $this is SubscriptionTopic) implies (%resource is Citation or %resource is Evidence or %resource is EvidenceReport or %resource is EvidenceVariable or %resource is MedicinalProductDefinition or %resource is PackagedProductDefinition or %resource is AdministrableProductDefinition or %resource is Ingredient or %resource is ClinicalUseDefinition or %resource is RegulatedAuthorization or %resource is SubstanceDefinition or %resource is SubscriptionStatus or %resource is SubscriptionTopic)}
+    <t xml:space="preserve">dom-r4b:R4リソース内に新しいR4Bリソースを含めると、インスタンスがR4システムと共有された場合に相互運用性の問題が発生する可能性があります / Containing new R4B resources within R4 resources may cause interoperability issues if instances are shared with R4 systems {($this is Citation or $this is Evidence or $this is EvidenceReport or $this is EvidenceVariable or $this is MedicinalProductDefinition or $this is PackagedProductDefinition or $this is AdministrableProductDefinition or $this is Ingredient or $this is ClinicalUseDefinition or $this is RegulatedAuthorization or $this is SubstanceDefinition or $this is SubscriptionStatus or $this is SubscriptionTopic) implies (%resource is Citation or %resource is Evidence or %resource is EvidenceReport or %resource is EvidenceVariable or %resource is MedicinalProductDefinition or %resource is PackagedProductDefinition or %resource is AdministrableProductDefinition or %resource is Ingredient or %resource is ClinicalUseDefinition or %resource is RegulatedAuthorization or %resource is SubstanceDefinition or %resource is SubscriptionStatus or %resource is SubscriptionTopic)}
 </t>
   </si>
   <si>
@@ -455,8 +455,8 @@
     <t>DomainResource.extension</t>
   </si>
   <si>
-    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-ext-1:Must have either extensions or value[x], not both {extension.exists() != value.exists()}</t>
+    <t>ele-1:すべてのFHIR要素は、@valueまたはchildrenを持っている必要があります。 / All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+ext-1:extensionまたはvalue[x]のいずれかが必要です。両方ではありません。 / Must have either extensions or value[x], not both {extension.exists() != value.exists()}</t>
   </si>
   <si>
     <t>MedicationAdministration.extension:requestDepartment</t>
@@ -479,8 +479,8 @@
 </t>
   </si>
   <si>
-    <t>ele-1:All FHIR elements must have a @value or children unless an empty Parameters resource {hasValue() or (children().count() &gt; id.count()) or $this is Parameters}
-ext-1:Must have either extensions or value[x], not both {extension.exists() != value.exists()}</t>
+    <t>ele-1:空のParametersリソースでない限り、すべてのFHIR要素には@valueまたはchildrenが必要です / All FHIR elements must have a @value or children unless an empty Parameters resource {hasValue() or (children().count() &gt; id.count()) or $this is Parameters}
+ext-1:両方ではなく、拡張または値[x]が必要です / Must have either extensions or value[x], not both {extension.exists() != value.exists()}</t>
   </si>
   <si>
     <t>MedicationAdministration.extension:requestAuthoredOn</t>
@@ -556,17 +556,17 @@
 user content</t>
   </si>
   <si>
-    <t>Extensions that cannot be ignored</t>
-  </si>
-  <si>
-    <t>May be used to represent additional information that is not part of the basic definition of the resource and that modifies the understanding of the element that contains it and/or the understanding of the containing element's descendants. Usually modifier elements provide negation or qualification. To make the use of extensions safe and manageable, there is a strict set of governance applied to the definition and use of extensions. Though any implementer is allowed to define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension. Applications processing a resource are required to check for modifier extensions.
+    <t>無視できない拡張機能 / Extensions that cannot be ignored</t>
+  </si>
+  <si>
+    <t>リソースの基本的な定義に含まれない、要素の理解や、それを含む要素の子孫の理解を修正する追加情報を表すためにも使用されることがあります。通常、修飾要素は否定や修飾を提供します。拡張機能の使用を安全で管理しやすくするために、拡張機能の定義と使用に対して厳格な統治が適用されます。実装者は拡張機能を定義することが許可されていますが、拡張機能の定義の一部として満たす必要がある要件があります。リソースを処理するアプリケーションは、修飾子拡張をチェックする必要があります。修飾子拡張は、リソースまたはドメインリソースの任意の要素の意味を変更してはなりません（修飾子拡張自体の意味も変更できません）。 / May be used to represent additional information that is not part of the basic definition of the resource and that modifies the understanding of the element that contains it and/or the understanding of the containing element's descendants. Usually modifier elements provide negation or qualification. To make the use of extensions safe and manageable, there is a strict set of governance applied to the definition and use of extensions. Though any implementer is allowed to define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension. Applications processing a resource are required to check for modifier extensions.
 Modifier extensions SHALL NOT change the meaning of any elements on Resource or DomainResource (including cannot change the meaning of modifierExtension itself).</t>
   </si>
   <si>
-    <t>There can be no stigma associated with the use of extensions by any application, project, or standard - regardless of the institution or jurisdiction that uses or defines the extensions.  The use of extensions is what allows the FHIR specification to retain a core level of simplicity for everyone.</t>
-  </si>
-  <si>
-    <t>Modifier extensions allow for extensions that *cannot* be safely ignored to be clearly distinguished from the vast majority of extensions which can be safely ignored.  This promotes interoperability by eliminating the need for implementers to prohibit the presence of extensions. For further information, see the [definition of modifier extensions](http://hl7.org/fhir/R4B/extensibility.html#modifierExtension).</t>
+    <t>どのようなアプリケーション、プロジェクト、または標準が拡張機能を使用しているかに関わらず、拡張機能の使用には決して汚名が付くわけではありません - それらを使用または定義する機関または管轄区域に関係なく。拡張機能の使用こそが、FHIR仕様を誰にとっても簡単なコアレベルで維持することを可能にします。 / There can be no stigma associated with the use of extensions by any application, project, or standard - regardless of the institution or jurisdiction that uses or defines the extensions.  The use of extensions is what allows the FHIR specification to retain a core level of simplicity for everyone.</t>
+  </si>
+  <si>
+    <t>修飾子拡張により、安全に無視できない拡張を、安全に無視できる大多数の拡張と明確に区別することができます。これにより、実装者が拡張の存在を禁止する必要がなくなり、相互運用性が促進されます。詳細については、[修飾子拡張の定義](http://hl7.org/fhir/R4B/extensibility.html#modifierExtension)を参照してください。 / Modifier extensions allow for extensions that *cannot* be safely ignored to be clearly distinguished from the vast majority of extensions which can be safely ignored.  This promotes interoperability by eliminating the need for implementers to prohibit the presence of extensions. For further information, see the [definition of modifier extensions](http://hl7.org/fhir/R4B/extensibility.html#modifierExtension).</t>
   </si>
   <si>
     <t>DomainResource.modifierExtension</t>
@@ -624,10 +624,10 @@
     <t>MedicationAdministration.identifier.id</t>
   </si>
   <si>
-    <t>Unique id for inter-element referencing</t>
-  </si>
-  <si>
-    <t>Unique id for the element within a resource (for internal references). This may be any string value that does not contain spaces.</t>
+    <t>要素間参照のための一意のID / Unique id for inter-element referencing</t>
+  </si>
+  <si>
+    <t>リソース内の要素の一意のID（内部参照用）。これは、スペースを含まない文字列値である場合があります。 / Unique id for the element within a resource (for internal references). This may be any string value that does not contain spaces.</t>
   </si>
   <si>
     <t>Element.id</t>
@@ -642,10 +642,13 @@
     <t>MedicationAdministration.identifier.extension</t>
   </si>
   <si>
-    <t>Additional content defined by implementations</t>
-  </si>
-  <si>
-    <t>May be used to represent additional information that is not part of the basic definition of the element. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
+    <t>実装で定義された追加のコンテンツ / Additional content defined by implementations</t>
+  </si>
+  <si>
+    <t>要素の基本的な定義の一部ではない追加情報を表すために使用できます。拡張機能を安全で管理しやすくするために、拡張機能の定義と使用に適用される厳格なガバナンスセットがあります。実装者は拡張機能を定義できますが、拡張機能の定義の一部として満たされる一連の要件があります。 / May be used to represent additional information that is not part of the basic definition of the element. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
+  </si>
+  <si>
+    <t>拡張機能を使用または定義する機関や管轄権に関係なく、アプリケーション、プロジェクト、または標準による拡張機能の使用に関連するスティグマはありません。拡張機能の使用は、FHIR仕様がすべての人にコアレベルのシンプルさを保持できるようにするものです。 / There can be no stigma associated with the use of extensions by any application, project, or standard - regardless of the institution or jurisdiction that uses or defines the extensions.  The use of extensions is what allows the FHIR specification to retain a core level of simplicity for everyone.</t>
   </si>
   <si>
     <t>Extensions are always sliced by (at least) url</t>
@@ -654,22 +657,26 @@
     <t>Element.extension</t>
   </si>
   <si>
+    <t>ele-1:すべてのFHIR要素には、@valueまたは子要素が必要です / All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+ext-1:両方ではなく、拡張または値[x]が必要です / Must have either extensions or value[x], not both {extension.exists() != value.exists()}</t>
+  </si>
+  <si>
     <t>MedicationAdministration.identifier:rpNumber.use</t>
   </si>
   <si>
     <t>MedicationAdministration.identifier.use</t>
   </si>
   <si>
-    <t>usual | official | temp | secondary | old (If known)</t>
-  </si>
-  <si>
-    <t>The purpose of this identifier.</t>
-  </si>
-  <si>
-    <t>Applications can assume that an identifier is permanent unless it explicitly says that it is temporary.</t>
-  </si>
-  <si>
-    <t>Allows the appropriate identifier for a particular context of use to be selected from among a set of identifiers.</t>
+    <t>通常|公式|一時的|セカンダリ|古い（知られている場合） / usual | official | temp | secondary | old (If known)</t>
+  </si>
+  <si>
+    <t>このidentifierの目的。 / The purpose of this identifier.</t>
+  </si>
+  <si>
+    <t>アプリケーションは、identifierが一時的なものであると明示的に言っていない限り、永続的であると想定できます。 / Applications can assume that an identifier is permanent unless it explicitly says that it is temporary.</t>
+  </si>
+  <si>
+    <t>特定の使用のコンテキストが一連のidentifierの中から選択される適切なidentifierを許可します。 / Allows the appropriate identifier for a particular context of use to be selected from among a set of identifiers.</t>
   </si>
   <si>
     <t>required</t>
@@ -679,6 +686,10 @@
   </si>
   <si>
     <t>Identifier.use</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ele-1:すべてのFHIR要素には、@valueまたは子要素が必要です / All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+</t>
   </si>
   <si>
     <t>Role.code or implied by context</t>
@@ -694,16 +705,16 @@
 </t>
   </si>
   <si>
-    <t>Description of identifier</t>
-  </si>
-  <si>
-    <t>A coded type for the identifier that can be used to determine which identifier to use for a specific purpose.</t>
-  </si>
-  <si>
-    <t>This element deals only with general categories of identifiers.  It SHOULD not be used for codes that correspond 1..1 with the Identifier.system. Some identifiers may fall into multiple categories due to common usage.   Where the system is known, a type is unnecessary because the type is always part of the system definition. However systems often need to handle identifiers where the system is not known. There is not a 1:1 relationship between type and system, since many different systems have the same type.</t>
-  </si>
-  <si>
-    <t>Allows users to make use of identifiers when the identifier system is not known.</t>
+    <t>identifierの説明 / Description of identifier</t>
+  </si>
+  <si>
+    <t>特定の目的に使用するidentifierを決定するために使用できるidentifierのコード化されたタイプ。 / A coded type for the identifier that can be used to determine which identifier to use for a specific purpose.</t>
+  </si>
+  <si>
+    <t>この要素は、identifierの一般的なカテゴリのみを扱います。identifier。システムに対応するコードに使用しないでください。一部のidentifierは、一般的な使用法により複数のカテゴリに分類される場合があります。システムがわかっている場合、タイプは常にシステム定義の一部であるため、タイプは不要です。ただし、システムが不明なidentifierを処理する必要があることがよくあります。多くの異なるシステムが同じタイプを持っているため、タイプとシステムの間に1：1の関係はありません。 / This element deals only with general categories of identifiers.  It SHOULD not be used for codes that correspond 1..1 with the Identifier.system. Some identifiers may fall into multiple categories due to common usage.   Where the system is known, a type is unnecessary because the type is always part of the system definition. However systems often need to handle identifiers where the system is not known. There is not a 1:1 relationship between type and system, since many different systems have the same type.</t>
+  </si>
+  <si>
+    <t>identifierシステムが不明な場合、ユーザーはidentifierを使用できます。 / Allows users to make use of identifiers when the identifier system is not known.</t>
   </si>
   <si>
     <t>extensible</t>
@@ -730,10 +741,10 @@
     <t>ここで付番されたIDがRp番号であることを明示するためにOID-urlとして定義された。http://jpfhir.jp/fhir/core/mhlw/IdSystem/Medication-RPGroupNumberで固定される。</t>
   </si>
   <si>
-    <t>Identifier.system is always case sensitive.</t>
-  </si>
-  <si>
-    <t>There are many sets  of identifiers.  To perform matching of two identifiers, we need to know what set we're dealing with. The system identifies a particular set of unique identifiers.</t>
+    <t>identifier。システムは常にケースに敏感です。 / Identifier.system is always case sensitive.</t>
+  </si>
+  <si>
+    <t>identifierのセットがたくさんあります。2つのidentifierを一致させるには、どのセットを扱っているかを知る必要があります。システムは、特定の一意のidentifierセットを識別します。 / There are many sets  of identifiers.  To perform matching of two identifiers, we need to know what set we're dealing with. The system identifies a particular set of unique identifiers.</t>
   </si>
   <si>
     <t>http://jpfhir.jp/fhir/core/mhlw/IdSystem/Medication-RPGroupNumber</t>
@@ -792,10 +803,10 @@
 </t>
   </si>
   <si>
-    <t>Time period when id is/was valid for use</t>
-  </si>
-  <si>
-    <t>Time period during which identifier is/was valid for use.</t>
+    <t>IDが使用に有効だった時間期間 / Time period when id is/was valid for use</t>
+  </si>
+  <si>
+    <t>identifierが使用される/有効な期間。 / Time period during which identifier is/was valid for use.</t>
   </si>
   <si>
     <t>Identifier.period</t>
@@ -817,13 +828,13 @@
 </t>
   </si>
   <si>
-    <t>Organization that issued id (may be just text)</t>
-  </si>
-  <si>
-    <t>Organization that issued/manages the identifier.</t>
-  </si>
-  <si>
-    <t>The Identifier.assigner may omit the .reference element and only contain a .display element reflecting the name or other textual information about the assigning organization.</t>
+    <t>IDを発行した組織（単なるテキストである可能性があります） / Organization that issued id (may be just text)</t>
+  </si>
+  <si>
+    <t>identifierを発行/管理する組織。 / Organization that issued/manages the identifier.</t>
+  </si>
+  <si>
+    <t>identifierは、.reference要素を省略し、割り当て組織に関する名前またはその他のテキスト情報を反映した.display要素のみを含む場合があります。 / The Identifier.assigner may omit the .reference element and only contain a .display element reflecting the name or other textual information about the assigning organization.</t>
   </si>
   <si>
     <t>Identifier.assigner</t>
@@ -847,7 +858,7 @@
     <t>薬剤をオーダする単位としての処方箋に対するID。原則として投薬実施の基となったMedicationRequestのIDを設定する。</t>
   </si>
   <si>
-    <t>This is a business identifier, not a resource identifier.</t>
+    <t>これはビジネスidentifierであり、リソースidentifierではありません。 / This is a business identifier, not a resource identifier.</t>
   </si>
   <si>
     <t>MedicationAdministration.identifier:requestIdentifier.id</t>
@@ -865,10 +876,10 @@
     <t>MedicationAdministration.identifier:requestIdentifier.system</t>
   </si>
   <si>
-    <t>The namespace for the identifier value</t>
-  </si>
-  <si>
-    <t>Establishes the namespace for the value - that is, a URL that describes a set values that are unique.</t>
+    <t>identifier値の名前空間 / The namespace for the identifier value</t>
+  </si>
+  <si>
+    <t>値の名前空間、つまり一意のセット値を記述するURLを確立します。 / Establishes the namespace for the value - that is, a URL that describes a set values that are unique.</t>
   </si>
   <si>
     <t>urn:oid:1.2.392.100495.20.3.11</t>
@@ -877,13 +888,13 @@
     <t>MedicationAdministration.identifier:requestIdentifier.value</t>
   </si>
   <si>
-    <t>The value that is unique</t>
-  </si>
-  <si>
-    <t>The portion of the identifier typically relevant to the user and which is unique within the context of the system.</t>
-  </si>
-  <si>
-    <t>If the value is a full URI, then the system SHALL be urn:ietf:rfc:3986.  The value's primary purpose is computational mapping.  As a result, it may be normalized for comparison purposes (e.g. removing non-significant whitespace, dashes, etc.)  A value formatted for human display can be conveyed using the [Rendered Value extension](http://hl7.org/fhir/R4B/extension-rendered-value.html). Identifier.value is to be treated as case sensitive unless knowledge of the Identifier.system allows the processer to be confident that non-case-sensitive processing is safe.</t>
+    <t>一意の値 / The value that is unique</t>
+  </si>
+  <si>
+    <t>通常、identifierの部分はユーザーに関連し、システムのコンテキスト内で一意のユーザーに関連しています。 / The portion of the identifier typically relevant to the user and which is unique within the context of the system.</t>
+  </si>
+  <si>
+    <t>値が完全なURIの場合、システムはurn：ietf：rfc：3986でなければなりません。値の主な目的は、計算マッピングです。その結果、比較目的で正規化される可能性があります（例えば、有意でない白文字、ダッシュなどの削除）ヒューマンディスプレイ用の値は、[レンダリングされた値拡張]（拡張レンダリングValue.html）を使用して伝達できます。identifier。価値は、identifierの知識を使用しない限り、ケースに敏感なものとして扱われます。システムにより、プロセッサーは、非セイズに固有の処理が安全であると確信できます。 / If the value is a full URI, then the system SHALL be urn:ietf:rfc:3986.  The value's primary purpose is computational mapping.  As a result, it may be normalized for comparison purposes (e.g. removing non-significant whitespace, dashes, etc.)  A value formatted for human display can be conveyed using the [Rendered Value extension](http://hl7.org/fhir/R4B/extension-rendered-value.html). Identifier.value is to be treated as case sensitive unless knowledge of the Identifier.system allows the processer to be confident that non-case-sensitive processing is safe.</t>
   </si>
   <si>
     <t>MedicationAdministration.identifier:requestIdentifier.period</t>
@@ -936,7 +947,7 @@
 【JP Core仕様】　completed or stopped に限定される。</t>
   </si>
   <si>
-    <t>This element is labeled as a modifier because the status contains codes that mark the resource as not currently valid.</t>
+    <t>この要素は修飾子としてラベル付けされています。なぜなら、ステータスには、リソースが現在無効であることを示すコードが含まれているためです。 / This element is labeled as a modifier because the status contains codes that mark the resource as not currently valid.</t>
   </si>
   <si>
     <t>患者への投与状況</t>
@@ -969,7 +980,7 @@
     <t>example</t>
   </si>
   <si>
-    <t>A set of codes indicating the reason why the MedicationAdministration is negated.</t>
+    <t>医薬品投与が取り消された理由を示すコードのセット / A set of codes indicating the reason why the MedicationAdministration is negated.</t>
   </si>
   <si>
     <t>http://hl7.org/fhir/ValueSet/reason-medication-not-given-codes|4.3.0</t>
@@ -990,10 +1001,10 @@
     <t>薬が使用される区分</t>
   </si>
   <si>
-    <t>Indicates where the medication is expected to be consumed or administered.</t>
-  </si>
-  <si>
-    <t>A coded concept describing where the medication administered is expected to occur.</t>
+    <t>薬剤の摂取または投与が予想される場所を示します。 / Indicates where the medication is expected to be consumed or administered.</t>
+  </si>
+  <si>
+    <t>薬剤の投与が予想される場所を記述するコード化された概念。 / A coded concept describing where the medication administered is expected to occur.</t>
   </si>
   <si>
     <t>http://hl7.org/fhir/ValueSet/medication-admin-category|4.3.0</t>
@@ -1042,10 +1053,10 @@
 </t>
   </si>
   <si>
-    <t>Who received medication</t>
-  </si>
-  <si>
-    <t>The person or animal or group receiving the medication.</t>
+    <t>誰が薬を受け取りましたか？ / Who received medication</t>
+  </si>
+  <si>
+    <t>薬を受け取る人、動物、またはグループ。 / The person or animal or group receiving the medication.</t>
   </si>
   <si>
     <t>Event.subject</t>
@@ -1067,10 +1078,10 @@
 </t>
   </si>
   <si>
-    <t>Encounter or Episode of Care administered as part of</t>
-  </si>
-  <si>
-    <t>The visit, admission, or other contact between patient and health care provider during which the medication administration was performed.</t>
+    <t>「エピソード・オブ・ケア」は、「エンカウンター」として提供されます。 / Encounter or Episode of Care administered as part of</t>
+  </si>
+  <si>
+    <t>薬剤投与が行われた患者と医療提供者の間での訪問、入院、またはその他の接触。 / The visit, admission, or other contact between patient and health care provider during which the medication administration was performed.</t>
   </si>
   <si>
     <t>Event.context</t>
@@ -1092,10 +1103,10 @@
 </t>
   </si>
   <si>
-    <t>Additional information to support administration</t>
-  </si>
-  <si>
-    <t>Additional information (for example, patient height and weight) that supports the administration of the medication.</t>
+    <t>管理をサポートするための追加情報 / Additional information to support administration</t>
+  </si>
+  <si>
+    <t>薬の投与を補助する追加情報（例えば、患者の身長や体重）。 / Additional information (for example, patient height and weight) that supports the administration of the medication.</t>
   </si>
   <si>
     <t>.outboundRelationship[typeCode=PERT].target[A_SupportingClinicalStatement CMET minimal with many different choices of classCodes(ORG, ENC, PROC, SPLY, SBADM, OBS) and each of the act class codes draws from one or more of the following moodCodes (EVN, DEF, INT PRMS, RQO, PRP, APT, ARQ, GOL)]</t>
@@ -1108,10 +1119,10 @@
 Period</t>
   </si>
   <si>
-    <t>Start and end time of administration</t>
-  </si>
-  <si>
-    <t>A specific date/time or interval of time during which the administration took place (or did not take place, when the 'notGiven' attribute is true). For many administrations, such as swallowing a tablet the use of dateTime is more appropriate.</t>
+    <t>管理の開始時刻と終了時刻 / Start and end time of administration</t>
+  </si>
+  <si>
+    <t>与えられた属性が「真実」となっている場合に、行政が行われた（または行われなかった）特定の日時または時間の間隔。錠剤の服用など、多くの行政では、dateTimeの使用が適切です。 / A specific date/time or interval of time during which the administration took place (or did not take place, when the 'notGiven' attribute is true). For many administrations, such as swallowing a tablet the use of dateTime is more appropriate.</t>
   </si>
   <si>
     <t>Event.occurrence[x]</t>
@@ -1133,13 +1144,13 @@
 </t>
   </si>
   <si>
-    <t>Who performed the medication administration and what they did</t>
-  </si>
-  <si>
-    <t>Indicates who or what performed the medication administration and how they were involved.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ele-1:All FHIR elements must have a @value or children unless an empty Parameters resource {hasValue() or (children().count() &gt; id.count()) or $this is Parameters}
+    <t>薬剤投与を行ったのは誰で、何をしたのか？ / Who performed the medication administration and what they did</t>
+  </si>
+  <si>
+    <t>薬の投与を行った人や物、および彼らがどのように関与したかを示す。 / Indicates who or what performed the medication administration and how they were involved.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ele-1:すべてのFHIR要素は、@valueまたはchildrenを持っている必要があります。 / All FHIR elements must have a @value or children unless an empty Parameters resource {hasValue() or (children().count() &gt; id.count()) or $this is Parameters}
 </t>
   </si>
   <si>
@@ -1158,7 +1169,19 @@
     <t>MedicationAdministration.performer.id</t>
   </si>
   <si>
+    <t>エレメント相互参照のためのユニークID / Unique id for inter-element referencing</t>
+  </si>
+  <si>
+    <t>リソース内の要素の固有ID（内部参照用）。これは、スペースを含まない任意の文字列値である可能性があります。 / Unique id for the element within a resource (for internal references). This may be any string value that does not contain spaces.</t>
+  </si>
+  <si>
     <t>MedicationAdministration.performer.extension</t>
+  </si>
+  <si>
+    <t>実装によって定義される追加コンテンツ / Additional content defined by implementations</t>
+  </si>
+  <si>
+    <t>要素の基本的な定義に含まれない追加情報を表すために使用されることがあります。拡張機能の使用を安全かつ管理しやすくするために、定義および使用に適用される厳格なガバナンスのセットがあります。実装者は拡張機能を定義できますが、拡張機能の定義の一部として満たす必要のある要件のセットがあります。 / May be used to represent additional information that is not part of the basic definition of the element. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
   </si>
   <si>
     <t>MedicationAdministration.performer.modifierExtension</t>
@@ -1168,10 +1191,11 @@
 user contentmodifiers</t>
   </si>
   <si>
-    <t>Extensions that cannot be ignored even if unrecognized</t>
-  </si>
-  <si>
-    <t>May be used to represent additional information that is not part of the basic definition of the element and that modifies the understanding of the element in which it is contained and/or the understanding of the containing element's descendants. Usually modifier elements provide negation or qualification. To make the use of extensions safe and manageable, there is a strict set of governance applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension. Applications processing a resource are required to check for modifier extensions.
+    <t>認識されなくても無視できない拡張機能 / Extensions that cannot be ignored even if unrecognized</t>
+  </si>
+  <si>
+    <t>基本的な要素の定義に含まれない追加情報を表すために使用されることがあり、それによって、その要素自体または取り込んでいる要素の子孫の理解を修正する。修飾子要素は通常、否定または修飾を提供します。拡張機能の安全で管理しやすい使用を実現するために、定義および使用に厳しいガバナンスセットが適用されています。どの実装者でも拡張機能を定義できますが、拡張機能の定義の一部として満たす必要がある要件があります。リソースを処理するアプリケーションは、修飾子拡張子をチェックする必要があります。
+修飾子拡張機能は、リソースまたはドメインリソースの任意の要素の意味を変更してはなりません（修飾子拡張自体の意味を変更することもできません）。 / May be used to represent additional information that is not part of the basic definition of the element and that modifies the understanding of the element in which it is contained and/or the understanding of the containing element's descendants. Usually modifier elements provide negation or qualification. To make the use of extensions safe and manageable, there is a strict set of governance applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension. Applications processing a resource are required to check for modifier extensions.
 Modifier extensions SHALL NOT change the meaning of any elements on Resource or DomainResource (including cannot change the meaning of modifierExtension itself).</t>
   </si>
   <si>
@@ -1181,13 +1205,13 @@
     <t>MedicationAdministration.performer.function</t>
   </si>
   <si>
-    <t>Type of performance</t>
-  </si>
-  <si>
-    <t>Distinguishes the type of involvement of the performer in the medication administration.</t>
-  </si>
-  <si>
-    <t>A code describing the role an individual played in administering the medication.</t>
+    <t>パフォーマンスの種類 / Type of performance</t>
+  </si>
+  <si>
+    <t>演者の医薬品投与における関与タイプを区別します。 / Distinguishes the type of involvement of the performer in the medication administration.</t>
+  </si>
+  <si>
+    <t>薬物管理を行った個人の役割を説明するコード / A code describing the role an individual played in administering the medication.</t>
   </si>
   <si>
     <t>http://hl7.org/fhir/ValueSet/med-admin-perform-function|4.3.0</t>
@@ -1206,10 +1230,10 @@
 </t>
   </si>
   <si>
-    <t>Who performed the medication administration</t>
-  </si>
-  <si>
-    <t>Indicates who or what performed the medication administration.</t>
+    <t>薬剤投与を行ったのは誰ですか？ / Who performed the medication administration</t>
+  </si>
+  <si>
+    <t>薬剤投与を行った人物または物品を示す / Indicates who or what performed the medication administration.</t>
   </si>
   <si>
     <t>Event.performer.actor</t>
@@ -1221,13 +1245,13 @@
     <t>MedicationAdministration.reasonCode</t>
   </si>
   <si>
-    <t>Reason administration performed</t>
-  </si>
-  <si>
-    <t>A code indicating why the medication was given.</t>
-  </si>
-  <si>
-    <t>A set of codes indicating the reason why the MedicationAdministration was made.</t>
+    <t>理由に基づく行政処理 / Reason administration performed</t>
+  </si>
+  <si>
+    <t>与えられた薬を説明するコード。 / A code indicating why the medication was given.</t>
+  </si>
+  <si>
+    <t>薬剤投与が行われた理由を示すコードのセット。 / A set of codes indicating the reason why the MedicationAdministration was made.</t>
   </si>
   <si>
     <t>http://hl7.org/fhir/ValueSet/reason-medication-given-codes|4.3.0</t>
@@ -1249,13 +1273,13 @@
 </t>
   </si>
   <si>
-    <t>Condition or observation that supports why the medication was administered</t>
-  </si>
-  <si>
-    <t>Condition or observation that supports why the medication was administered.</t>
-  </si>
-  <si>
-    <t>This is a reference to a condition that is the reason for the medication request.  If only a code exists, use reasonCode.</t>
+    <t>薬が投与された理由を支持する状態または観察 / Condition or observation that supports why the medication was administered</t>
+  </si>
+  <si>
+    <t>薬剤が投与された理由を支持する状態または観察。 / Condition or observation that supports why the medication was administered.</t>
+  </si>
+  <si>
+    <t>これは、薬剤依頼の理由となる状態に関する参照です。もしコードしか存在しない場合は、reasonCodeを使用してください。 / This is a reference to a condition that is the reason for the medication request.  If only a code exists, use reasonCode.</t>
   </si>
   <si>
     <t>Event.reasonReference</t>
@@ -1277,13 +1301,13 @@
 </t>
   </si>
   <si>
-    <t>Request administration performed against</t>
-  </si>
-  <si>
-    <t>The original request, instruction or authority to perform the administration.</t>
-  </si>
-  <si>
-    <t>This is a reference to the MedicationRequest  where the intent is either order or instance-order.  It should not reference MedicationRequests where the intent is any other value.</t>
+    <t>リクエスト管理対象として実行してください。 / Request administration performed against</t>
+  </si>
+  <si>
+    <t>管理を実行するための元の要求、指示、または権限。 / The original request, instruction or authority to perform the administration.</t>
+  </si>
+  <si>
+    <t>これは、意図がオーダーまたはインスタンスオーダーであるMedicationRequestへの参照であり、意図が他の値であるMedicationRequestへの参照ではありません。 / This is a reference to the MedicationRequest  where the intent is either order or instance-order.  It should not reference MedicationRequests where the intent is any other value.</t>
   </si>
   <si>
     <t>Event.basedOn</t>
@@ -1302,10 +1326,10 @@
 </t>
   </si>
   <si>
-    <t>Device used to administer</t>
-  </si>
-  <si>
-    <t>The device used in administering the medication to the patient.  For example, a particular infusion pump.</t>
+    <t>投与するための装置 / Device used to administer</t>
+  </si>
+  <si>
+    <t>患者に薬剤を投与するのに使われる装置。例えば、特定の注入ポンプ。 / The device used in administering the medication to the patient.  For example, a particular infusion pump.</t>
   </si>
   <si>
     <t>device-&gt;Access  OR device-&gt;AssignedDevice</t>
@@ -1321,10 +1345,10 @@
 </t>
   </si>
   <si>
-    <t>Information about the administration</t>
-  </si>
-  <si>
-    <t>Extra information about the medication administration that is not conveyed by the other attributes.</t>
+    <t>行政に関する情報 / Information about the administration</t>
+  </si>
+  <si>
+    <t>他の属性では伝えられない薬剤投与に関する追加情報 / Extra information about the medication administration that is not conveyed by the other attributes.</t>
   </si>
   <si>
     <t>Event.note</t>
@@ -1342,8 +1366,8 @@
     <t>投薬量情報の詳細を説明する。線量、率、場所、ルートなど。</t>
   </si>
   <si>
-    <t>ele-1:All FHIR elements must have a @value or children unless an empty Parameters resource {hasValue() or (children().count() &gt; id.count()) or $this is Parameters}
-mad-1:SHALL have at least one of dosage.dose or dosage.rate[x] {dose.exists() or rate.exists()}</t>
+    <t>ele-1:すべてのFHIR要素は、@valueまたはchildrenを持っている必要があります。 / All FHIR elements must have a @value or children unless an empty Parameters resource {hasValue() or (children().count() &gt; id.count()) or $this is Parameters}
+mad-1:「用量、投与回数、投与速度[x] のうち少なくとも1つを有するものとする」と訳すことができます。 / SHALL have at least one of dosage.dose or dosage.rate[x] {dose.exists() or rate.exists()}</t>
   </si>
   <si>
     <t>component-&gt;SubstanceAdministrationEvent</t>
@@ -1517,16 +1541,16 @@
 </t>
   </si>
   <si>
-    <t>Code defined by a terminology system</t>
-  </si>
-  <si>
-    <t>A reference to a code defined by a terminology system.</t>
-  </si>
-  <si>
-    <t>Codes may be defined very casually in enumerations, or code lists, up to very formal definitions such as SNOMED CT - see the HL7 v3 Core Principles for more information.  Ordering of codings is undefined and SHALL NOT be used to infer meaning. Generally, at most only one of the coding values will be labeled as UserSelected = true.</t>
-  </si>
-  <si>
-    <t>Allows for alternative encodings within a code system, and translations to other code systems.</t>
+    <t>用語システムによって定義されたコード / Code defined by a terminology system</t>
+  </si>
+  <si>
+    <t>用語システムによって定義されたコードへの参照。 / A reference to a code defined by a terminology system.</t>
+  </si>
+  <si>
+    <t>コードは、列挙されたCTなどの非常に正式な定義まで、列挙またはコードリストで非常にさりげなく定義される場合があります。詳細については、HL7 V3コアプリンシップを参照してください。コーディングの順序付けは未定義であり、意味を推測するために使用されません。一般に、せいぜい、コーディング値の1つのみがuserselected = trueとしてラベル付けされます。 / Codes may be defined very casually in enumerations, or code lists, up to very formal definitions such as SNOMED CT - see the HL7 v3 Core Principles for more information.  Ordering of codings is undefined and SHALL NOT be used to infer meaning. Generally, at most only one of the coding values will be labeled as UserSelected = true.</t>
+  </si>
+  <si>
+    <t>コードシステム内の代替エンコーディング、および他のコードシステムへの翻訳が可能になります。 / Allows for alternative encodings within a code system, and translations to other code systems.</t>
   </si>
   <si>
     <t>CodeableConcept.coding</t>
@@ -1541,16 +1565,16 @@
     <t>MedicationAdministration.dosage.site.text</t>
   </si>
   <si>
-    <t>Plain text representation of the concept</t>
-  </si>
-  <si>
-    <t>A human language representation of the concept as seen/selected/uttered by the user who entered the data and/or which represents the intended meaning of the user.</t>
-  </si>
-  <si>
-    <t>Very often the text is the same as a displayName of one of the codings.</t>
-  </si>
-  <si>
-    <t>The codes from the terminologies do not always capture the correct meaning with all the nuances of the human using them, or sometimes there is no appropriate code at all. In these cases, the text is used to capture the full meaning of the source.</t>
+    <t>コンセプトの単純なテキスト表現 / Plain text representation of the concept</t>
+  </si>
+  <si>
+    <t>データを入力したユーザー、および/またはユーザーの意図された意味を表すユーザーによって見られる/選択/発言された概念の人間の言語表現。 / A human language representation of the concept as seen/selected/uttered by the user who entered the data and/or which represents the intended meaning of the user.</t>
+  </si>
+  <si>
+    <t>多くの場合、テキストはコーディングの1つの表示名と同じです。 / Very often the text is the same as a displayName of one of the codings.</t>
+  </si>
+  <si>
+    <t>用語からのコードは、それらを使用する人間のすべてのニュアンスを使用して、常に正しい意味をキャプチャするとは限りません。または、適切なコードがまったくない場合があります。これらの場合、テキストはソースの完全な意味をキャプチャするために使用されます。 / The codes from the terminologies do not always capture the correct meaning with all the nuances of the human using them, or sometimes there is no appropriate code at all. In these cases, the text is used to capture the full meaning of the source.</t>
   </si>
   <si>
     <t>CodeableConcept.text</t>
@@ -1620,7 +1644,7 @@
     <t>コード化された値は体内に薬剤が投与される方法を示している。注射ではよく使われる。たとえば、緩徐に注入、深部に静注など。</t>
   </si>
   <si>
-    <t>A coded concept describing the technique by which the medicine is administered.</t>
+    <t>薬剤が投与される方法を記述する暗号化された概念。 / A coded concept describing the technique by which the medicine is administered.</t>
   </si>
   <si>
     <t>http://hl7.org/fhir/ValueSet/administration-method-codes|4.3.0</t>
@@ -1696,16 +1720,16 @@
     <t>MedicationAdministration.dosage.method.coding.system</t>
   </si>
   <si>
-    <t>Identity of the terminology system</t>
-  </si>
-  <si>
-    <t>The identification of the code system that defines the meaning of the symbol in the code.</t>
-  </si>
-  <si>
-    <t>The URI may be an OID (urn:oid:...) or a UUID (urn:uuid:...).  OIDs and UUIDs SHALL be references to the HL7 OID registry. Otherwise, the URI should come from HL7's list of FHIR defined special URIs or it should reference to some definition that establishes the system clearly and unambiguously.</t>
-  </si>
-  <si>
-    <t>Need to be unambiguous about the source of the definition of the symbol.</t>
+    <t>用語システムのアイデンティティ / Identity of the terminology system</t>
+  </si>
+  <si>
+    <t>コード内のシンボルの意味を定義するコードシステムの識別。 / The identification of the code system that defines the meaning of the symbol in the code.</t>
+  </si>
+  <si>
+    <t>uriは、oid（urn：oid：...）またはuuid（urn：uuid：...）である場合があります。OIDとUUIDは、HL7 OIDレジストリへの参照となります。それ以外の場合、URIは、FHIRの特別なURIを定義したHL7のリストから来るか、システムを明確かつ明確に確立する定義を参照する必要があります。 / The URI may be an OID (urn:oid:...) or a UUID (urn:uuid:...).  OIDs and UUIDs SHALL be references to the HL7 OID registry. Otherwise, the URI should come from HL7's list of FHIR defined special URIs or it should reference to some definition that establishes the system clearly and unambiguously.</t>
+  </si>
+  <si>
+    <t>シンボルの定義のソースについて明確である必要があります。 / Need to be unambiguous about the source of the definition of the symbol.</t>
   </si>
   <si>
     <t>http://jami.jp/CodeSystem/MedicationMethodBasicUsage</t>
@@ -1726,13 +1750,13 @@
     <t>MedicationAdministration.dosage.method.coding.version</t>
   </si>
   <si>
-    <t>Version of the system - if relevant</t>
-  </si>
-  <si>
-    <t>The version of the code system which was used when choosing this code. Note that a well-maintained code system does not need the version reported, because the meaning of codes is consistent across versions. However this cannot consistently be assured, and when the meaning is not guaranteed to be consistent, the version SHOULD be exchanged.</t>
-  </si>
-  <si>
-    <t>Where the terminology does not clearly define what string should be used to identify code system versions, the recommendation is to use the date (expressed in FHIR date format) on which that version was officially published as the version date.</t>
+    <t>システムのバージョン - 関連する場合 / Version of the system - if relevant</t>
+  </si>
+  <si>
+    <t>このコードを選択するときに使用されたコードシステムのバージョン。コードの意味がバージョン全体で一貫しているため、適切にメンテナンスしたコードシステムでは報告されたバージョンを必要としないことに注意してください。ただし、これは一貫して保証することはできず、意味が一貫していることが保証されていない場合、バージョンを交換する必要があります。 / The version of the code system which was used when choosing this code. Note that a well-maintained code system does not need the version reported, because the meaning of codes is consistent across versions. However this cannot consistently be assured, and when the meaning is not guaranteed to be consistent, the version SHOULD be exchanged.</t>
+  </si>
+  <si>
+    <t>用語がコードシステムバージョンを識別するために使用する文字列を明確に定義していない場合、推奨は、そのバージョンがバージョンの日付として公式に公開された日付（FHIR日付形式で表現）を使用することです。 / Where the terminology does not clearly define what string should be used to identify code system versions, the recommendation is to use the date (expressed in FHIR date format) on which that version was officially published as the version date.</t>
   </si>
   <si>
     <t>Coding.version</t>
@@ -1750,13 +1774,13 @@
     <t>MedicationAdministration.dosage.method.coding.code</t>
   </si>
   <si>
-    <t>Symbol in syntax defined by the system</t>
-  </si>
-  <si>
-    <t>A symbol in syntax defined by the system. The symbol may be a predefined code or an expression in a syntax defined by the coding system (e.g. post-coordination).</t>
-  </si>
-  <si>
-    <t>Need to refer to a particular code in the system.</t>
+    <t>システムによって定義された構文のシンボル / Symbol in syntax defined by the system</t>
+  </si>
+  <si>
+    <t>システムによって定義された構文のシンボル。シンボルは、定義されたコードまたはコーディングシステムによって定義された構文の式（例：調整後）である場合があります。 / A symbol in syntax defined by the system. The symbol may be a predefined code or an expression in a syntax defined by the coding system (e.g. post-coordination).</t>
+  </si>
+  <si>
+    <t>システム内の特定のコードを参照する必要があります。 / Need to refer to a particular code in the system.</t>
   </si>
   <si>
     <t>Coding.code</t>
@@ -1774,13 +1798,13 @@
     <t>MedicationAdministration.dosage.method.coding.display</t>
   </si>
   <si>
-    <t>Representation defined by the system</t>
-  </si>
-  <si>
-    <t>A representation of the meaning of the code in the system, following the rules of the system.</t>
-  </si>
-  <si>
-    <t>Need to be able to carry a human-readable meaning of the code for readers that do not know  the system.</t>
+    <t>システムによって定義された表現 / Representation defined by the system</t>
+  </si>
+  <si>
+    <t>システムのルールに従って、システム内のコードの意味の表現。 / A representation of the meaning of the code in the system, following the rules of the system.</t>
+  </si>
+  <si>
+    <t>システムを知らない読者のために、コードの人間の読み取り可能な意味を持ち込むことができる必要があります。 / Need to be able to carry a human-readable meaning of the code for readers that do not know  the system.</t>
   </si>
   <si>
     <t>Coding.display</t>
@@ -1802,16 +1826,16 @@
 </t>
   </si>
   <si>
-    <t>If this coding was chosen directly by the user</t>
-  </si>
-  <si>
-    <t>Indicates that this coding was chosen by a user directly - e.g. off a pick list of available items (codes or displays).</t>
-  </si>
-  <si>
-    <t>Amongst a set of alternatives, a directly chosen code is the most appropriate starting point for new translations. There is some ambiguity about what exactly 'directly chosen' implies, and trading partner agreement may be needed to clarify the use of this element and its consequences more completely.</t>
-  </si>
-  <si>
-    <t>This has been identified as a clinical safety criterium - that this exact system/code pair was chosen explicitly, rather than inferred by the system based on some rules or language processing.</t>
+    <t>このコーディングがユーザーによって直接選択された場合 / If this coding was chosen directly by the user</t>
+  </si>
+  <si>
+    <t>このコーディングがユーザーによって直接選択されたことを示します。利用可能なアイテムのピックリスト（コードまたはディスプレイ）。 / Indicates that this coding was chosen by a user directly - e.g. off a pick list of available items (codes or displays).</t>
+  </si>
+  <si>
+    <t>一連の代替案の中で、直接選択されたコードが新しい翻訳の最も適切な出発点です。この要素の使用とその結果をより完全に明確にするためには、「直接選択された」ことについては曖昧さがあり、取引パートナー契約が必要になる場合があります。 / Amongst a set of alternatives, a directly chosen code is the most appropriate starting point for new translations. There is some ambiguity about what exactly 'directly chosen' implies, and trading partner agreement may be needed to clarify the use of this element and its consequences more completely.</t>
+  </si>
+  <si>
+    <t>これは、臨床安全基準として特定されています - この正確なシステム/コードペアは、いくつかのルールまたは言語処理に基づいてシステムによって推測されるのではなく、明示的に選択されたことです。 / This has been identified as a clinical safety criterium - that this exact system/code pair was chosen explicitly, rather than inferred by the system based on some rules or language processing.</t>
   </si>
   <si>
     <t>Coding.userSelected</t>
@@ -1890,7 +1914,7 @@
     <t>1回の投与イベントで投与される薬剤の量。この値は、投与が錠剤の飲み込みや注射などの本質的に瞬間的なイベントである場合に使用する。</t>
   </si>
   <si>
-    <t>If the administration is not instantaneous (rate is present), this can be specified to convey the total amount administered over period of time of a single administration.</t>
+    <t>もし投与速度が即時でない場合、単回の投与期間中に投与される総量を示すことができます。 / If the administration is not instantaneous (rate is present), this can be specified to convey the total amount administered over period of time of a single administration.</t>
   </si>
   <si>
     <t>.doseQuantity</t>
@@ -1939,13 +1963,13 @@
 </t>
   </si>
   <si>
-    <t>Dose quantity per unit of time</t>
-  </si>
-  <si>
-    <t>Identifies the speed with which the medication was or will be introduced into the patient.  Typically, the rate for an infusion e.g. 100 ml per 1 hour or 100 ml/hr.  May also be expressed as a rate per unit of time, e.g. 500 ml per 2 hours.  Other examples:  200 mcg/min or 200 mcg/1 minute; 1 liter/8 hours.</t>
-  </si>
-  <si>
-    <t>If the rate changes over time, and you want to capture this in MedicationAdministration, then each change should be captured as a distinct MedicationAdministration, with a specific MedicationAdministration.dosage.rate, and the date time when the rate change occurred. Typically, the MedicationAdministration.dosage.rate element is not used to convey an average rate.</t>
+    <t>時間当たりの投与量 / Dose quantity per unit of time</t>
+  </si>
+  <si>
+    <t>薬剤が患者に投与された速度または投与される速度を識別します。通常、輸液の場合は1時間あたり100mlまたは100ml/hrなどの速度です。時間の単位あたりの速度として表現することもできます（例：2時間あたり500ml）。その他の例：200 mcg/分または200 mcg/1分、1リットル/8時間。 / Identifies the speed with which the medication was or will be introduced into the patient.  Typically, the rate for an infusion e.g. 100 ml per 1 hour or 100 ml/hr.  May also be expressed as a rate per unit of time, e.g. 500 ml per 2 hours.  Other examples:  200 mcg/min or 200 mcg/1 minute; 1 liter/8 hours.</t>
+  </si>
+  <si>
+    <t>もしレートが時間の経過とともに変化する場合、かつそれをMedicationAdministrationに取り込む場合は、それぞれの変化を特定のMedicationAdministration.dosage.rateと、レート変更が発生した日時で捉える必要があります。通常、MedicationAdministration.dosage.rate要素は平均レートを伝えるために使用されません。 / If the rate changes over time, and you want to capture this in MedicationAdministration, then each change should be captured as a distinct MedicationAdministration, with a specific MedicationAdministration.dosage.rate, and the date time when the rate change occurred. Typically, the MedicationAdministration.dosage.rate element is not used to convey an average rate.</t>
   </si>
   <si>
     <t>MedicationAdministration.dosage.rate[x]:rateQuantity</t>
@@ -1974,7 +1998,7 @@
     <t>投与が確認されたときなど、発生した関連のあるベントのサマリー。</t>
   </si>
   <si>
-    <t>This might not include provenances for all versions of the request – only those deemed “relevant” or important. This SHALL NOT include the Provenance associated with this current version of the resource. (If that provenance is deemed to be a “relevant” change, it will need to be added as part of a later update. Until then, it can be queried directly as the Provenance that points to this version using _revinclude All Provenances should have some historical version of this Request as their subject.</t>
+    <t>この要請のすべてのバージョンの起源が含まれているわけではない可能性があります。ただし、「関連性」または重要と見なされるものに限定されます。それに含まれる証跡には、このリソースの現在のバージョンに関連するものは含まれません。 （そのプロバイナンスが「関連性のある」変更である場合、後の更新の一部として追加する必要があります。その時までは、このバージョンを指すプロバイナンスとして直接クエリできます。All Provenancesは、この要求の過去のバージョンを主題として持つ必要があります。 / This might not include provenances for all versions of the request – only those deemed “relevant” or important. This SHALL NOT include the Provenance associated with this current version of the resource. (If that provenance is deemed to be a “relevant” change, it will need to be added as part of a later update. Until then, it can be queried directly as the Provenance that points to this version using _revinclude All Provenances should have some historical version of this Request as their subject.</t>
   </si>
   <si>
     <t>.inboundRelationship(typeCode=SUBJ].source[classCode=CACT, moodCode=EVN]</t>
@@ -2308,7 +2332,7 @@
     <col min="22" max="22" width="15.13671875" customWidth="true" bestFit="true"/>
     <col min="23" max="23" width="16.3203125" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="16.16796875" customWidth="true" bestFit="true"/>
-    <col min="25" max="25" width="68.23828125" customWidth="true" bestFit="true"/>
+    <col min="25" max="25" width="96.17578125" customWidth="true" bestFit="true"/>
     <col min="26" max="26" width="59.3515625" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
@@ -4469,7 +4493,7 @@
         <v>200</v>
       </c>
       <c r="N19" t="s" s="2">
-        <v>174</v>
+        <v>201</v>
       </c>
       <c r="O19" s="2"/>
       <c r="P19" t="s" s="2">
@@ -4510,7 +4534,7 @@
         <v>139</v>
       </c>
       <c r="AC19" t="s" s="2">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="AD19" t="s" s="2">
         <v>79</v>
@@ -4519,7 +4543,7 @@
         <v>140</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>80</v>
@@ -4531,7 +4555,7 @@
         <v>79</v>
       </c>
       <c r="AJ19" t="s" s="2">
-        <v>142</v>
+        <v>204</v>
       </c>
       <c r="AK19" t="s" s="2">
         <v>79</v>
@@ -4551,10 +4575,10 @@
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -4580,16 +4604,16 @@
         <v>110</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="N20" t="s" s="2">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="O20" t="s" s="2">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="P20" t="s" s="2">
         <v>79</v>
@@ -4614,11 +4638,11 @@
         <v>79</v>
       </c>
       <c r="X20" t="s" s="2">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="Y20" s="2"/>
       <c r="Z20" t="s" s="2">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="AA20" t="s" s="2">
         <v>79</v>
@@ -4636,7 +4660,7 @@
         <v>79</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>80</v>
@@ -4648,13 +4672,13 @@
         <v>79</v>
       </c>
       <c r="AJ20" t="s" s="2">
-        <v>102</v>
+        <v>214</v>
       </c>
       <c r="AK20" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AL20" t="s" s="2">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="AM20" t="s" s="2">
         <v>79</v>
@@ -4668,10 +4692,10 @@
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>214</v>
+        <v>217</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -4694,19 +4718,19 @@
         <v>91</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c r="N21" t="s" s="2">
-        <v>218</v>
+        <v>221</v>
       </c>
       <c r="O21" t="s" s="2">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="P21" t="s" s="2">
         <v>79</v>
@@ -4731,11 +4755,11 @@
         <v>79</v>
       </c>
       <c r="X21" t="s" s="2">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="Y21" s="2"/>
       <c r="Z21" t="s" s="2">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="AA21" t="s" s="2">
         <v>79</v>
@@ -4753,7 +4777,7 @@
         <v>79</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>222</v>
+        <v>225</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>80</v>
@@ -4765,19 +4789,19 @@
         <v>79</v>
       </c>
       <c r="AJ21" t="s" s="2">
-        <v>102</v>
+        <v>214</v>
       </c>
       <c r="AK21" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AL21" t="s" s="2">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="AM21" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AN21" t="s" s="2">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="AO21" t="s" s="2">
         <v>79</v>
@@ -4785,10 +4809,10 @@
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -4814,29 +4838,29 @@
         <v>104</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="N22" t="s" s="2">
-        <v>228</v>
+        <v>231</v>
       </c>
       <c r="O22" t="s" s="2">
-        <v>229</v>
+        <v>232</v>
       </c>
       <c r="P22" t="s" s="2">
         <v>79</v>
       </c>
       <c r="Q22" s="2"/>
       <c r="R22" t="s" s="2">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="S22" t="s" s="2">
         <v>79</v>
       </c>
       <c r="T22" t="s" s="2">
-        <v>231</v>
+        <v>234</v>
       </c>
       <c r="U22" t="s" s="2">
         <v>79</v>
@@ -4872,7 +4896,7 @@
         <v>79</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>232</v>
+        <v>235</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>80</v>
@@ -4884,19 +4908,19 @@
         <v>79</v>
       </c>
       <c r="AJ22" t="s" s="2">
-        <v>102</v>
+        <v>214</v>
       </c>
       <c r="AK22" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AL22" t="s" s="2">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="AM22" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AN22" t="s" s="2">
-        <v>234</v>
+        <v>237</v>
       </c>
       <c r="AO22" t="s" s="2">
         <v>79</v>
@@ -4904,10 +4928,10 @@
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>235</v>
+        <v>238</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>236</v>
+        <v>239</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -4930,16 +4954,16 @@
         <v>91</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>237</v>
+        <v>240</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>238</v>
+        <v>241</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>239</v>
+        <v>242</v>
       </c>
       <c r="N23" t="s" s="2">
-        <v>240</v>
+        <v>243</v>
       </c>
       <c r="O23" s="2"/>
       <c r="P23" t="s" s="2">
@@ -4953,7 +4977,7 @@
         <v>79</v>
       </c>
       <c r="T23" t="s" s="2">
-        <v>241</v>
+        <v>244</v>
       </c>
       <c r="U23" t="s" s="2">
         <v>79</v>
@@ -4989,7 +5013,7 @@
         <v>79</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>242</v>
+        <v>245</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>80</v>
@@ -5001,19 +5025,19 @@
         <v>79</v>
       </c>
       <c r="AJ23" t="s" s="2">
-        <v>102</v>
+        <v>214</v>
       </c>
       <c r="AK23" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AL23" t="s" s="2">
-        <v>243</v>
+        <v>246</v>
       </c>
       <c r="AM23" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AN23" t="s" s="2">
-        <v>244</v>
+        <v>247</v>
       </c>
       <c r="AO23" t="s" s="2">
         <v>79</v>
@@ -5021,10 +5045,10 @@
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
-        <v>245</v>
+        <v>248</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>246</v>
+        <v>249</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -5047,13 +5071,13 @@
         <v>91</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>247</v>
+        <v>250</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="N24" s="2"/>
       <c r="O24" s="2"/>
@@ -5104,7 +5128,7 @@
         <v>79</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>80</v>
@@ -5116,19 +5140,19 @@
         <v>79</v>
       </c>
       <c r="AJ24" t="s" s="2">
-        <v>102</v>
+        <v>214</v>
       </c>
       <c r="AK24" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AL24" t="s" s="2">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="AM24" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AN24" t="s" s="2">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c r="AO24" t="s" s="2">
         <v>79</v>
@@ -5136,10 +5160,10 @@
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>254</v>
+        <v>257</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -5162,16 +5186,16 @@
         <v>91</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>256</v>
+        <v>259</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c r="N25" t="s" s="2">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="O25" s="2"/>
       <c r="P25" t="s" s="2">
@@ -5221,7 +5245,7 @@
         <v>79</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>80</v>
@@ -5233,19 +5257,19 @@
         <v>79</v>
       </c>
       <c r="AJ25" t="s" s="2">
-        <v>102</v>
+        <v>214</v>
       </c>
       <c r="AK25" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AL25" t="s" s="2">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="AM25" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AN25" t="s" s="2">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="AO25" t="s" s="2">
         <v>79</v>
@@ -5253,13 +5277,13 @@
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="B26" t="s" s="2">
         <v>177</v>
       </c>
       <c r="C26" t="s" s="2">
-        <v>263</v>
+        <v>266</v>
       </c>
       <c r="D26" t="s" s="2">
         <v>79</v>
@@ -5284,13 +5308,13 @@
         <v>178</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="N26" t="s" s="2">
-        <v>266</v>
+        <v>269</v>
       </c>
       <c r="O26" s="2"/>
       <c r="P26" t="s" s="2">
@@ -5372,7 +5396,7 @@
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>267</v>
+        <v>270</v>
       </c>
       <c r="B27" t="s" s="2">
         <v>192</v>
@@ -5487,7 +5511,7 @@
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="B28" t="s" s="2">
         <v>198</v>
@@ -5522,7 +5546,7 @@
         <v>200</v>
       </c>
       <c r="N28" t="s" s="2">
-        <v>174</v>
+        <v>201</v>
       </c>
       <c r="O28" s="2"/>
       <c r="P28" t="s" s="2">
@@ -5563,7 +5587,7 @@
         <v>139</v>
       </c>
       <c r="AC28" t="s" s="2">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="AD28" t="s" s="2">
         <v>79</v>
@@ -5572,7 +5596,7 @@
         <v>140</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>80</v>
@@ -5584,7 +5608,7 @@
         <v>79</v>
       </c>
       <c r="AJ28" t="s" s="2">
-        <v>142</v>
+        <v>204</v>
       </c>
       <c r="AK28" t="s" s="2">
         <v>79</v>
@@ -5604,10 +5628,10 @@
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
-        <v>269</v>
+        <v>272</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -5633,16 +5657,16 @@
         <v>110</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="N29" t="s" s="2">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="O29" t="s" s="2">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="P29" t="s" s="2">
         <v>79</v>
@@ -5667,11 +5691,11 @@
         <v>79</v>
       </c>
       <c r="X29" t="s" s="2">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="Y29" s="2"/>
       <c r="Z29" t="s" s="2">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="AA29" t="s" s="2">
         <v>79</v>
@@ -5689,7 +5713,7 @@
         <v>79</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>80</v>
@@ -5701,13 +5725,13 @@
         <v>79</v>
       </c>
       <c r="AJ29" t="s" s="2">
-        <v>102</v>
+        <v>214</v>
       </c>
       <c r="AK29" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AL29" t="s" s="2">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="AM29" t="s" s="2">
         <v>79</v>
@@ -5721,10 +5745,10 @@
     </row>
     <row r="30">
       <c r="A30" t="s" s="2">
-        <v>270</v>
+        <v>273</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>214</v>
+        <v>217</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -5747,19 +5771,19 @@
         <v>91</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c r="N30" t="s" s="2">
-        <v>218</v>
+        <v>221</v>
       </c>
       <c r="O30" t="s" s="2">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="P30" t="s" s="2">
         <v>79</v>
@@ -5784,11 +5808,11 @@
         <v>79</v>
       </c>
       <c r="X30" t="s" s="2">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="Y30" s="2"/>
       <c r="Z30" t="s" s="2">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="AA30" t="s" s="2">
         <v>79</v>
@@ -5806,7 +5830,7 @@
         <v>79</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>222</v>
+        <v>225</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>80</v>
@@ -5818,19 +5842,19 @@
         <v>79</v>
       </c>
       <c r="AJ30" t="s" s="2">
-        <v>102</v>
+        <v>214</v>
       </c>
       <c r="AK30" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AL30" t="s" s="2">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="AM30" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AN30" t="s" s="2">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="AO30" t="s" s="2">
         <v>79</v>
@@ -5838,10 +5862,10 @@
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>271</v>
+        <v>274</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -5867,29 +5891,29 @@
         <v>104</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>272</v>
+        <v>275</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>273</v>
+        <v>276</v>
       </c>
       <c r="N31" t="s" s="2">
-        <v>228</v>
+        <v>231</v>
       </c>
       <c r="O31" t="s" s="2">
-        <v>229</v>
+        <v>232</v>
       </c>
       <c r="P31" t="s" s="2">
         <v>79</v>
       </c>
       <c r="Q31" s="2"/>
       <c r="R31" t="s" s="2">
-        <v>274</v>
+        <v>277</v>
       </c>
       <c r="S31" t="s" s="2">
         <v>79</v>
       </c>
       <c r="T31" t="s" s="2">
-        <v>231</v>
+        <v>234</v>
       </c>
       <c r="U31" t="s" s="2">
         <v>79</v>
@@ -5925,7 +5949,7 @@
         <v>79</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>232</v>
+        <v>235</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>80</v>
@@ -5937,19 +5961,19 @@
         <v>79</v>
       </c>
       <c r="AJ31" t="s" s="2">
-        <v>102</v>
+        <v>214</v>
       </c>
       <c r="AK31" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AL31" t="s" s="2">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="AM31" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AN31" t="s" s="2">
-        <v>234</v>
+        <v>237</v>
       </c>
       <c r="AO31" t="s" s="2">
         <v>79</v>
@@ -5957,10 +5981,10 @@
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
-        <v>275</v>
+        <v>278</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>236</v>
+        <v>239</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -5983,16 +6007,16 @@
         <v>91</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>237</v>
+        <v>240</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>276</v>
+        <v>279</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="N32" t="s" s="2">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="O32" s="2"/>
       <c r="P32" t="s" s="2">
@@ -6006,7 +6030,7 @@
         <v>79</v>
       </c>
       <c r="T32" t="s" s="2">
-        <v>241</v>
+        <v>244</v>
       </c>
       <c r="U32" t="s" s="2">
         <v>79</v>
@@ -6042,7 +6066,7 @@
         <v>79</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>242</v>
+        <v>245</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>80</v>
@@ -6054,19 +6078,19 @@
         <v>79</v>
       </c>
       <c r="AJ32" t="s" s="2">
-        <v>102</v>
+        <v>214</v>
       </c>
       <c r="AK32" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AL32" t="s" s="2">
-        <v>243</v>
+        <v>246</v>
       </c>
       <c r="AM32" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AN32" t="s" s="2">
-        <v>244</v>
+        <v>247</v>
       </c>
       <c r="AO32" t="s" s="2">
         <v>79</v>
@@ -6074,10 +6098,10 @@
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
-        <v>279</v>
+        <v>282</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>246</v>
+        <v>249</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -6100,13 +6124,13 @@
         <v>91</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>247</v>
+        <v>250</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="N33" s="2"/>
       <c r="O33" s="2"/>
@@ -6157,7 +6181,7 @@
         <v>79</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>80</v>
@@ -6169,19 +6193,19 @@
         <v>79</v>
       </c>
       <c r="AJ33" t="s" s="2">
-        <v>102</v>
+        <v>214</v>
       </c>
       <c r="AK33" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AL33" t="s" s="2">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="AM33" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AN33" t="s" s="2">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c r="AO33" t="s" s="2">
         <v>79</v>
@@ -6189,10 +6213,10 @@
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>254</v>
+        <v>257</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -6215,16 +6239,16 @@
         <v>91</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>256</v>
+        <v>259</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c r="N34" t="s" s="2">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="O34" s="2"/>
       <c r="P34" t="s" s="2">
@@ -6274,7 +6298,7 @@
         <v>79</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>80</v>
@@ -6286,19 +6310,19 @@
         <v>79</v>
       </c>
       <c r="AJ34" t="s" s="2">
-        <v>102</v>
+        <v>214</v>
       </c>
       <c r="AK34" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AL34" t="s" s="2">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="AM34" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AN34" t="s" s="2">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="AO34" t="s" s="2">
         <v>79</v>
@@ -6306,10 +6330,10 @@
     </row>
     <row r="35">
       <c r="A35" t="s" s="2">
-        <v>281</v>
+        <v>284</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>281</v>
+        <v>284</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -6335,10 +6359,10 @@
         <v>104</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>282</v>
+        <v>285</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="N35" s="2"/>
       <c r="O35" s="2"/>
@@ -6389,7 +6413,7 @@
         <v>79</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>281</v>
+        <v>284</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>80</v>
@@ -6404,10 +6428,10 @@
         <v>102</v>
       </c>
       <c r="AK35" t="s" s="2">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="AL35" t="s" s="2">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="AM35" t="s" s="2">
         <v>79</v>
@@ -6421,10 +6445,10 @@
     </row>
     <row r="36">
       <c r="A36" t="s" s="2">
-        <v>286</v>
+        <v>289</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>286</v>
+        <v>289</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -6447,13 +6471,13 @@
         <v>91</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>287</v>
+        <v>290</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>288</v>
+        <v>291</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>289</v>
+        <v>292</v>
       </c>
       <c r="N36" s="2"/>
       <c r="O36" s="2"/>
@@ -6504,7 +6528,7 @@
         <v>79</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>286</v>
+        <v>289</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>80</v>
@@ -6519,10 +6543,10 @@
         <v>102</v>
       </c>
       <c r="AK36" t="s" s="2">
-        <v>290</v>
+        <v>293</v>
       </c>
       <c r="AL36" t="s" s="2">
-        <v>291</v>
+        <v>294</v>
       </c>
       <c r="AM36" t="s" s="2">
         <v>79</v>
@@ -6536,10 +6560,10 @@
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
-        <v>292</v>
+        <v>295</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>292</v>
+        <v>295</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -6565,13 +6589,13 @@
         <v>110</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>293</v>
+        <v>296</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>294</v>
+        <v>297</v>
       </c>
       <c r="N37" t="s" s="2">
-        <v>295</v>
+        <v>298</v>
       </c>
       <c r="O37" s="2"/>
       <c r="P37" t="s" s="2">
@@ -6597,13 +6621,13 @@
         <v>79</v>
       </c>
       <c r="X37" t="s" s="2">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="Y37" t="s" s="2">
-        <v>296</v>
+        <v>299</v>
       </c>
       <c r="Z37" t="s" s="2">
-        <v>297</v>
+        <v>300</v>
       </c>
       <c r="AA37" t="s" s="2">
         <v>79</v>
@@ -6621,7 +6645,7 @@
         <v>79</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>292</v>
+        <v>295</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>90</v>
@@ -6636,16 +6660,16 @@
         <v>102</v>
       </c>
       <c r="AK37" t="s" s="2">
-        <v>298</v>
+        <v>301</v>
       </c>
       <c r="AL37" t="s" s="2">
-        <v>299</v>
+        <v>302</v>
       </c>
       <c r="AM37" t="s" s="2">
-        <v>300</v>
+        <v>303</v>
       </c>
       <c r="AN37" t="s" s="2">
-        <v>301</v>
+        <v>304</v>
       </c>
       <c r="AO37" t="s" s="2">
         <v>79</v>
@@ -6653,10 +6677,10 @@
     </row>
     <row r="38">
       <c r="A38" t="s" s="2">
-        <v>302</v>
+        <v>305</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>302</v>
+        <v>305</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -6679,13 +6703,13 @@
         <v>79</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>303</v>
+        <v>306</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>304</v>
+        <v>307</v>
       </c>
       <c r="N38" s="2"/>
       <c r="O38" s="2"/>
@@ -6712,31 +6736,31 @@
         <v>79</v>
       </c>
       <c r="X38" t="s" s="2">
+        <v>308</v>
+      </c>
+      <c r="Y38" t="s" s="2">
+        <v>309</v>
+      </c>
+      <c r="Z38" t="s" s="2">
+        <v>310</v>
+      </c>
+      <c r="AA38" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AB38" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AC38" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AD38" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AE38" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AF38" t="s" s="2">
         <v>305</v>
-      </c>
-      <c r="Y38" t="s" s="2">
-        <v>306</v>
-      </c>
-      <c r="Z38" t="s" s="2">
-        <v>307</v>
-      </c>
-      <c r="AA38" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AB38" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AC38" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AD38" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AE38" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AF38" t="s" s="2">
-        <v>302</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>80</v>
@@ -6751,16 +6775,16 @@
         <v>102</v>
       </c>
       <c r="AK38" t="s" s="2">
-        <v>308</v>
+        <v>311</v>
       </c>
       <c r="AL38" t="s" s="2">
-        <v>309</v>
+        <v>312</v>
       </c>
       <c r="AM38" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AN38" t="s" s="2">
-        <v>310</v>
+        <v>313</v>
       </c>
       <c r="AO38" t="s" s="2">
         <v>79</v>
@@ -6768,10 +6792,10 @@
     </row>
     <row r="39">
       <c r="A39" t="s" s="2">
-        <v>311</v>
+        <v>314</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>311</v>
+        <v>314</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -6794,13 +6818,13 @@
         <v>79</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>312</v>
+        <v>315</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>313</v>
+        <v>316</v>
       </c>
       <c r="N39" s="2"/>
       <c r="O39" s="2"/>
@@ -6830,28 +6854,28 @@
         <v>114</v>
       </c>
       <c r="Y39" t="s" s="2">
+        <v>317</v>
+      </c>
+      <c r="Z39" t="s" s="2">
+        <v>318</v>
+      </c>
+      <c r="AA39" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AB39" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AC39" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AD39" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AE39" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AF39" t="s" s="2">
         <v>314</v>
-      </c>
-      <c r="Z39" t="s" s="2">
-        <v>315</v>
-      </c>
-      <c r="AA39" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AB39" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AC39" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AD39" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AE39" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AF39" t="s" s="2">
-        <v>311</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>80</v>
@@ -6869,7 +6893,7 @@
         <v>79</v>
       </c>
       <c r="AL39" t="s" s="2">
-        <v>316</v>
+        <v>319</v>
       </c>
       <c r="AM39" t="s" s="2">
         <v>79</v>
@@ -6883,10 +6907,10 @@
     </row>
     <row r="40">
       <c r="A40" t="s" s="2">
-        <v>317</v>
+        <v>320</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>317</v>
+        <v>320</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -6909,16 +6933,16 @@
         <v>91</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>318</v>
+        <v>321</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>319</v>
+        <v>322</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>320</v>
+        <v>323</v>
       </c>
       <c r="N40" t="s" s="2">
-        <v>321</v>
+        <v>324</v>
       </c>
       <c r="O40" s="2"/>
       <c r="P40" t="s" s="2">
@@ -6968,7 +6992,7 @@
         <v>79</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>317</v>
+        <v>320</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>90</v>
@@ -6983,16 +7007,16 @@
         <v>102</v>
       </c>
       <c r="AK40" t="s" s="2">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="AL40" t="s" s="2">
-        <v>323</v>
+        <v>326</v>
       </c>
       <c r="AM40" t="s" s="2">
-        <v>324</v>
+        <v>327</v>
       </c>
       <c r="AN40" t="s" s="2">
-        <v>325</v>
+        <v>328</v>
       </c>
       <c r="AO40" t="s" s="2">
         <v>79</v>
@@ -7000,10 +7024,10 @@
     </row>
     <row r="41">
       <c r="A41" t="s" s="2">
-        <v>326</v>
+        <v>329</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>326</v>
+        <v>329</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -7026,13 +7050,13 @@
         <v>91</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>327</v>
+        <v>330</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>328</v>
+        <v>331</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>329</v>
+        <v>332</v>
       </c>
       <c r="N41" s="2"/>
       <c r="O41" s="2"/>
@@ -7083,7 +7107,7 @@
         <v>79</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>326</v>
+        <v>329</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>90</v>
@@ -7098,16 +7122,16 @@
         <v>102</v>
       </c>
       <c r="AK41" t="s" s="2">
-        <v>330</v>
+        <v>333</v>
       </c>
       <c r="AL41" t="s" s="2">
-        <v>331</v>
+        <v>334</v>
       </c>
       <c r="AM41" t="s" s="2">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="AN41" t="s" s="2">
-        <v>333</v>
+        <v>336</v>
       </c>
       <c r="AO41" t="s" s="2">
         <v>79</v>
@@ -7115,10 +7139,10 @@
     </row>
     <row r="42">
       <c r="A42" t="s" s="2">
-        <v>334</v>
+        <v>337</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>334</v>
+        <v>337</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -7141,13 +7165,13 @@
         <v>79</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>335</v>
+        <v>338</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>336</v>
+        <v>339</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>337</v>
+        <v>340</v>
       </c>
       <c r="N42" s="2"/>
       <c r="O42" s="2"/>
@@ -7198,7 +7222,7 @@
         <v>79</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>334</v>
+        <v>337</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>80</v>
@@ -7213,16 +7237,16 @@
         <v>102</v>
       </c>
       <c r="AK42" t="s" s="2">
-        <v>338</v>
+        <v>341</v>
       </c>
       <c r="AL42" t="s" s="2">
-        <v>339</v>
+        <v>342</v>
       </c>
       <c r="AM42" t="s" s="2">
-        <v>340</v>
+        <v>343</v>
       </c>
       <c r="AN42" t="s" s="2">
-        <v>341</v>
+        <v>344</v>
       </c>
       <c r="AO42" t="s" s="2">
         <v>79</v>
@@ -7230,10 +7254,10 @@
     </row>
     <row r="43">
       <c r="A43" t="s" s="2">
-        <v>342</v>
+        <v>345</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>342</v>
+        <v>345</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -7256,13 +7280,13 @@
         <v>79</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>344</v>
+        <v>347</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>345</v>
+        <v>348</v>
       </c>
       <c r="N43" s="2"/>
       <c r="O43" s="2"/>
@@ -7313,7 +7337,7 @@
         <v>79</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>342</v>
+        <v>345</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>80</v>
@@ -7331,10 +7355,10 @@
         <v>79</v>
       </c>
       <c r="AL43" t="s" s="2">
-        <v>346</v>
+        <v>349</v>
       </c>
       <c r="AM43" t="s" s="2">
-        <v>340</v>
+        <v>343</v>
       </c>
       <c r="AN43" t="s" s="2">
         <v>79</v>
@@ -7345,10 +7369,10 @@
     </row>
     <row r="44">
       <c r="A44" t="s" s="2">
-        <v>347</v>
+        <v>350</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>347</v>
+        <v>350</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -7371,13 +7395,13 @@
         <v>91</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>348</v>
+        <v>351</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>349</v>
+        <v>352</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>350</v>
+        <v>353</v>
       </c>
       <c r="N44" s="2"/>
       <c r="O44" s="2"/>
@@ -7428,7 +7452,7 @@
         <v>79</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>347</v>
+        <v>350</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>90</v>
@@ -7443,16 +7467,16 @@
         <v>102</v>
       </c>
       <c r="AK44" t="s" s="2">
-        <v>351</v>
+        <v>354</v>
       </c>
       <c r="AL44" t="s" s="2">
-        <v>352</v>
+        <v>355</v>
       </c>
       <c r="AM44" t="s" s="2">
-        <v>353</v>
+        <v>356</v>
       </c>
       <c r="AN44" t="s" s="2">
-        <v>354</v>
+        <v>357</v>
       </c>
       <c r="AO44" t="s" s="2">
         <v>79</v>
@@ -7460,10 +7484,10 @@
     </row>
     <row r="45">
       <c r="A45" t="s" s="2">
-        <v>355</v>
+        <v>358</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>355</v>
+        <v>358</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -7486,13 +7510,13 @@
         <v>91</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>356</v>
+        <v>359</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>357</v>
+        <v>360</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="N45" s="2"/>
       <c r="O45" s="2"/>
@@ -7543,7 +7567,7 @@
         <v>79</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>355</v>
+        <v>358</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>80</v>
@@ -7555,19 +7579,19 @@
         <v>79</v>
       </c>
       <c r="AJ45" t="s" s="2">
-        <v>359</v>
+        <v>362</v>
       </c>
       <c r="AK45" t="s" s="2">
-        <v>360</v>
+        <v>363</v>
       </c>
       <c r="AL45" t="s" s="2">
-        <v>361</v>
+        <v>364</v>
       </c>
       <c r="AM45" t="s" s="2">
-        <v>362</v>
+        <v>365</v>
       </c>
       <c r="AN45" t="s" s="2">
-        <v>363</v>
+        <v>366</v>
       </c>
       <c r="AO45" t="s" s="2">
         <v>79</v>
@@ -7575,10 +7599,10 @@
     </row>
     <row r="46">
       <c r="A46" t="s" s="2">
-        <v>364</v>
+        <v>367</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>364</v>
+        <v>367</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -7601,13 +7625,13 @@
         <v>79</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>237</v>
+        <v>240</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>193</v>
+        <v>368</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>194</v>
+        <v>369</v>
       </c>
       <c r="N46" s="2"/>
       <c r="O46" s="2"/>
@@ -7690,10 +7714,10 @@
     </row>
     <row r="47">
       <c r="A47" t="s" s="2">
-        <v>365</v>
+        <v>370</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>365</v>
+        <v>370</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -7719,10 +7743,10 @@
         <v>136</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>199</v>
+        <v>371</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>200</v>
+        <v>372</v>
       </c>
       <c r="N47" t="s" s="2">
         <v>174</v>
@@ -7775,7 +7799,7 @@
         <v>79</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>80</v>
@@ -7807,14 +7831,14 @@
     </row>
     <row r="48">
       <c r="A48" t="s" s="2">
-        <v>366</v>
+        <v>373</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>366</v>
+        <v>373</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
-        <v>367</v>
+        <v>374</v>
       </c>
       <c r="E48" s="2"/>
       <c r="F48" t="s" s="2">
@@ -7836,10 +7860,10 @@
         <v>136</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>368</v>
+        <v>375</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>369</v>
+        <v>376</v>
       </c>
       <c r="N48" t="s" s="2">
         <v>174</v>
@@ -7894,7 +7918,7 @@
         <v>79</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>370</v>
+        <v>377</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>80</v>
@@ -7926,10 +7950,10 @@
     </row>
     <row r="49">
       <c r="A49" t="s" s="2">
-        <v>371</v>
+        <v>378</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>371</v>
+        <v>378</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -7952,13 +7976,13 @@
         <v>79</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>372</v>
+        <v>379</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>373</v>
+        <v>380</v>
       </c>
       <c r="N49" s="2"/>
       <c r="O49" s="2"/>
@@ -7985,13 +8009,13 @@
         <v>79</v>
       </c>
       <c r="X49" t="s" s="2">
-        <v>305</v>
+        <v>308</v>
       </c>
       <c r="Y49" t="s" s="2">
-        <v>374</v>
+        <v>381</v>
       </c>
       <c r="Z49" t="s" s="2">
-        <v>375</v>
+        <v>382</v>
       </c>
       <c r="AA49" t="s" s="2">
         <v>79</v>
@@ -8009,7 +8033,7 @@
         <v>79</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>371</v>
+        <v>378</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>80</v>
@@ -8024,10 +8048,10 @@
         <v>102</v>
       </c>
       <c r="AK49" t="s" s="2">
-        <v>376</v>
+        <v>383</v>
       </c>
       <c r="AL49" t="s" s="2">
-        <v>377</v>
+        <v>384</v>
       </c>
       <c r="AM49" t="s" s="2">
         <v>79</v>
@@ -8041,10 +8065,10 @@
     </row>
     <row r="50">
       <c r="A50" t="s" s="2">
-        <v>378</v>
+        <v>385</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>378</v>
+        <v>385</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -8067,13 +8091,13 @@
         <v>91</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>379</v>
+        <v>386</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>380</v>
+        <v>387</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>381</v>
+        <v>388</v>
       </c>
       <c r="N50" s="2"/>
       <c r="O50" s="2"/>
@@ -8124,7 +8148,7 @@
         <v>79</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>378</v>
+        <v>385</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>90</v>
@@ -8139,10 +8163,10 @@
         <v>102</v>
       </c>
       <c r="AK50" t="s" s="2">
-        <v>382</v>
+        <v>389</v>
       </c>
       <c r="AL50" t="s" s="2">
-        <v>383</v>
+        <v>390</v>
       </c>
       <c r="AM50" t="s" s="2">
         <v>79</v>
@@ -8156,10 +8180,10 @@
     </row>
     <row r="51">
       <c r="A51" t="s" s="2">
-        <v>384</v>
+        <v>391</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>384</v>
+        <v>391</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -8182,13 +8206,13 @@
         <v>79</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>385</v>
+        <v>392</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>386</v>
+        <v>393</v>
       </c>
       <c r="N51" s="2"/>
       <c r="O51" s="2"/>
@@ -8215,13 +8239,13 @@
         <v>79</v>
       </c>
       <c r="X51" t="s" s="2">
-        <v>305</v>
+        <v>308</v>
       </c>
       <c r="Y51" t="s" s="2">
-        <v>387</v>
+        <v>394</v>
       </c>
       <c r="Z51" t="s" s="2">
-        <v>388</v>
+        <v>395</v>
       </c>
       <c r="AA51" t="s" s="2">
         <v>79</v>
@@ -8239,7 +8263,7 @@
         <v>79</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>384</v>
+        <v>391</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>80</v>
@@ -8254,16 +8278,16 @@
         <v>102</v>
       </c>
       <c r="AK51" t="s" s="2">
-        <v>389</v>
+        <v>396</v>
       </c>
       <c r="AL51" t="s" s="2">
-        <v>390</v>
+        <v>397</v>
       </c>
       <c r="AM51" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AN51" t="s" s="2">
-        <v>391</v>
+        <v>398</v>
       </c>
       <c r="AO51" t="s" s="2">
         <v>79</v>
@@ -8271,10 +8295,10 @@
     </row>
     <row r="52">
       <c r="A52" t="s" s="2">
-        <v>392</v>
+        <v>399</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>392</v>
+        <v>399</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -8297,16 +8321,16 @@
         <v>79</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>393</v>
+        <v>400</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>394</v>
+        <v>401</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>395</v>
+        <v>402</v>
       </c>
       <c r="N52" t="s" s="2">
-        <v>396</v>
+        <v>403</v>
       </c>
       <c r="O52" s="2"/>
       <c r="P52" t="s" s="2">
@@ -8356,7 +8380,7 @@
         <v>79</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>392</v>
+        <v>399</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>80</v>
@@ -8371,27 +8395,27 @@
         <v>102</v>
       </c>
       <c r="AK52" t="s" s="2">
-        <v>397</v>
+        <v>404</v>
       </c>
       <c r="AL52" t="s" s="2">
-        <v>398</v>
+        <v>405</v>
       </c>
       <c r="AM52" t="s" s="2">
-        <v>399</v>
+        <v>406</v>
       </c>
       <c r="AN52" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AO52" t="s" s="2">
-        <v>400</v>
+        <v>407</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="s" s="2">
-        <v>401</v>
+        <v>408</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>401</v>
+        <v>408</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -8414,16 +8438,16 @@
         <v>79</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>402</v>
+        <v>409</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>403</v>
+        <v>410</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>404</v>
+        <v>411</v>
       </c>
       <c r="N53" t="s" s="2">
-        <v>405</v>
+        <v>412</v>
       </c>
       <c r="O53" s="2"/>
       <c r="P53" t="s" s="2">
@@ -8473,7 +8497,7 @@
         <v>79</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>401</v>
+        <v>408</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>80</v>
@@ -8488,16 +8512,16 @@
         <v>102</v>
       </c>
       <c r="AK53" t="s" s="2">
-        <v>406</v>
+        <v>413</v>
       </c>
       <c r="AL53" t="s" s="2">
-        <v>407</v>
+        <v>414</v>
       </c>
       <c r="AM53" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AN53" t="s" s="2">
-        <v>408</v>
+        <v>415</v>
       </c>
       <c r="AO53" t="s" s="2">
         <v>79</v>
@@ -8505,10 +8529,10 @@
     </row>
     <row r="54">
       <c r="A54" t="s" s="2">
-        <v>409</v>
+        <v>416</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>409</v>
+        <v>416</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -8531,13 +8555,13 @@
         <v>79</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>410</v>
+        <v>417</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>411</v>
+        <v>418</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>412</v>
+        <v>419</v>
       </c>
       <c r="N54" s="2"/>
       <c r="O54" s="2"/>
@@ -8588,7 +8612,7 @@
         <v>79</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>409</v>
+        <v>416</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>80</v>
@@ -8606,13 +8630,13 @@
         <v>79</v>
       </c>
       <c r="AL54" t="s" s="2">
-        <v>413</v>
+        <v>420</v>
       </c>
       <c r="AM54" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AN54" t="s" s="2">
-        <v>414</v>
+        <v>421</v>
       </c>
       <c r="AO54" t="s" s="2">
         <v>79</v>
@@ -8620,10 +8644,10 @@
     </row>
     <row r="55">
       <c r="A55" t="s" s="2">
-        <v>415</v>
+        <v>422</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>415</v>
+        <v>422</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -8646,13 +8670,13 @@
         <v>79</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>416</v>
+        <v>423</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>417</v>
+        <v>424</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>418</v>
+        <v>425</v>
       </c>
       <c r="N55" s="2"/>
       <c r="O55" s="2"/>
@@ -8703,7 +8727,7 @@
         <v>79</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>415</v>
+        <v>422</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>80</v>
@@ -8718,10 +8742,10 @@
         <v>102</v>
       </c>
       <c r="AK55" t="s" s="2">
-        <v>419</v>
+        <v>426</v>
       </c>
       <c r="AL55" t="s" s="2">
-        <v>420</v>
+        <v>427</v>
       </c>
       <c r="AM55" t="s" s="2">
         <v>79</v>
@@ -8735,10 +8759,10 @@
     </row>
     <row r="56">
       <c r="A56" t="s" s="2">
-        <v>421</v>
+        <v>428</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>421</v>
+        <v>428</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -8761,13 +8785,13 @@
         <v>79</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>356</v>
+        <v>359</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>422</v>
+        <v>429</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>423</v>
+        <v>430</v>
       </c>
       <c r="N56" s="2"/>
       <c r="O56" s="2"/>
@@ -8818,7 +8842,7 @@
         <v>79</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>421</v>
+        <v>428</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>80</v>
@@ -8830,13 +8854,13 @@
         <v>79</v>
       </c>
       <c r="AJ56" t="s" s="2">
-        <v>424</v>
+        <v>431</v>
       </c>
       <c r="AK56" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AL56" t="s" s="2">
-        <v>425</v>
+        <v>432</v>
       </c>
       <c r="AM56" t="s" s="2">
         <v>79</v>
@@ -8850,10 +8874,10 @@
     </row>
     <row r="57">
       <c r="A57" t="s" s="2">
-        <v>426</v>
+        <v>433</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>426</v>
+        <v>433</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -8876,13 +8900,13 @@
         <v>79</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>237</v>
+        <v>240</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>193</v>
+        <v>368</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>194</v>
+        <v>369</v>
       </c>
       <c r="N57" s="2"/>
       <c r="O57" s="2"/>
@@ -8965,10 +8989,10 @@
     </row>
     <row r="58">
       <c r="A58" t="s" s="2">
-        <v>427</v>
+        <v>434</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>427</v>
+        <v>434</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -9046,7 +9070,7 @@
         <v>140</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>80</v>
@@ -9078,13 +9102,13 @@
     </row>
     <row r="59">
       <c r="A59" t="s" s="2">
-        <v>428</v>
+        <v>435</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>427</v>
+        <v>434</v>
       </c>
       <c r="C59" t="s" s="2">
-        <v>429</v>
+        <v>436</v>
       </c>
       <c r="D59" t="s" s="2">
         <v>79</v>
@@ -9106,13 +9130,13 @@
         <v>79</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>430</v>
+        <v>437</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>431</v>
+        <v>438</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>432</v>
+        <v>439</v>
       </c>
       <c r="N59" s="2"/>
       <c r="O59" s="2"/>
@@ -9163,7 +9187,7 @@
         <v>79</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>80</v>
@@ -9195,13 +9219,13 @@
     </row>
     <row r="60">
       <c r="A60" t="s" s="2">
-        <v>433</v>
+        <v>440</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>427</v>
+        <v>434</v>
       </c>
       <c r="C60" t="s" s="2">
-        <v>434</v>
+        <v>441</v>
       </c>
       <c r="D60" t="s" s="2">
         <v>79</v>
@@ -9223,13 +9247,13 @@
         <v>79</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>435</v>
+        <v>442</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>436</v>
+        <v>443</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>437</v>
+        <v>444</v>
       </c>
       <c r="N60" s="2"/>
       <c r="O60" s="2"/>
@@ -9280,7 +9304,7 @@
         <v>79</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>80</v>
@@ -9312,13 +9336,13 @@
     </row>
     <row r="61">
       <c r="A61" t="s" s="2">
-        <v>438</v>
+        <v>445</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>427</v>
+        <v>434</v>
       </c>
       <c r="C61" t="s" s="2">
-        <v>439</v>
+        <v>446</v>
       </c>
       <c r="D61" t="s" s="2">
         <v>79</v>
@@ -9340,13 +9364,13 @@
         <v>79</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>440</v>
+        <v>447</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>441</v>
+        <v>448</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>442</v>
+        <v>449</v>
       </c>
       <c r="N61" s="2"/>
       <c r="O61" s="2"/>
@@ -9397,7 +9421,7 @@
         <v>79</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>80</v>
@@ -9429,13 +9453,13 @@
     </row>
     <row r="62">
       <c r="A62" t="s" s="2">
-        <v>443</v>
+        <v>450</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>427</v>
+        <v>434</v>
       </c>
       <c r="C62" t="s" s="2">
-        <v>444</v>
+        <v>451</v>
       </c>
       <c r="D62" t="s" s="2">
         <v>79</v>
@@ -9457,13 +9481,13 @@
         <v>79</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>445</v>
+        <v>452</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>446</v>
+        <v>453</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>447</v>
+        <v>454</v>
       </c>
       <c r="N62" s="2"/>
       <c r="O62" s="2"/>
@@ -9514,7 +9538,7 @@
         <v>79</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>80</v>
@@ -9546,13 +9570,13 @@
     </row>
     <row r="63">
       <c r="A63" t="s" s="2">
-        <v>448</v>
+        <v>455</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>427</v>
+        <v>434</v>
       </c>
       <c r="C63" t="s" s="2">
-        <v>449</v>
+        <v>456</v>
       </c>
       <c r="D63" t="s" s="2">
         <v>79</v>
@@ -9574,13 +9598,13 @@
         <v>79</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>450</v>
+        <v>457</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>451</v>
+        <v>458</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>452</v>
+        <v>459</v>
       </c>
       <c r="N63" s="2"/>
       <c r="O63" s="2"/>
@@ -9631,7 +9655,7 @@
         <v>79</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>80</v>
@@ -9663,14 +9687,14 @@
     </row>
     <row r="64">
       <c r="A64" t="s" s="2">
-        <v>453</v>
+        <v>460</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>453</v>
+        <v>460</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
-        <v>367</v>
+        <v>374</v>
       </c>
       <c r="E64" s="2"/>
       <c r="F64" t="s" s="2">
@@ -9692,10 +9716,10 @@
         <v>136</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>368</v>
+        <v>375</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>369</v>
+        <v>376</v>
       </c>
       <c r="N64" t="s" s="2">
         <v>174</v>
@@ -9750,7 +9774,7 @@
         <v>79</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>370</v>
+        <v>377</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>80</v>
@@ -9782,10 +9806,10 @@
     </row>
     <row r="65">
       <c r="A65" t="s" s="2">
-        <v>454</v>
+        <v>461</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>454</v>
+        <v>461</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -9808,13 +9832,13 @@
         <v>79</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>237</v>
+        <v>240</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>455</v>
+        <v>462</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>456</v>
+        <v>463</v>
       </c>
       <c r="N65" s="2"/>
       <c r="O65" s="2"/>
@@ -9865,7 +9889,7 @@
         <v>79</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>454</v>
+        <v>461</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>80</v>
@@ -9883,7 +9907,7 @@
         <v>79</v>
       </c>
       <c r="AL65" t="s" s="2">
-        <v>457</v>
+        <v>464</v>
       </c>
       <c r="AM65" t="s" s="2">
         <v>79</v>
@@ -9897,10 +9921,10 @@
     </row>
     <row r="66">
       <c r="A66" t="s" s="2">
-        <v>458</v>
+        <v>465</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>458</v>
+        <v>465</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -9923,16 +9947,16 @@
         <v>79</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>459</v>
+        <v>466</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>460</v>
+        <v>467</v>
       </c>
       <c r="N66" t="s" s="2">
-        <v>461</v>
+        <v>468</v>
       </c>
       <c r="O66" s="2"/>
       <c r="P66" t="s" s="2">
@@ -9962,7 +9986,7 @@
       </c>
       <c r="Y66" s="2"/>
       <c r="Z66" t="s" s="2">
-        <v>462</v>
+        <v>469</v>
       </c>
       <c r="AA66" t="s" s="2">
         <v>79</v>
@@ -9980,7 +10004,7 @@
         <v>79</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>458</v>
+        <v>465</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>80</v>
@@ -9998,13 +10022,13 @@
         <v>79</v>
       </c>
       <c r="AL66" t="s" s="2">
-        <v>463</v>
+        <v>470</v>
       </c>
       <c r="AM66" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AN66" t="s" s="2">
-        <v>464</v>
+        <v>471</v>
       </c>
       <c r="AO66" t="s" s="2">
         <v>79</v>
@@ -10012,10 +10036,10 @@
     </row>
     <row r="67">
       <c r="A67" t="s" s="2">
-        <v>465</v>
+        <v>472</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>465</v>
+        <v>472</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -10127,10 +10151,10 @@
     </row>
     <row r="68">
       <c r="A68" t="s" s="2">
-        <v>466</v>
+        <v>473</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>466</v>
+        <v>473</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -10162,7 +10186,7 @@
         <v>200</v>
       </c>
       <c r="N68" t="s" s="2">
-        <v>174</v>
+        <v>201</v>
       </c>
       <c r="O68" s="2"/>
       <c r="P68" t="s" s="2">
@@ -10203,7 +10227,7 @@
         <v>139</v>
       </c>
       <c r="AC68" t="s" s="2">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="AD68" t="s" s="2">
         <v>79</v>
@@ -10212,7 +10236,7 @@
         <v>140</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>80</v>
@@ -10224,7 +10248,7 @@
         <v>79</v>
       </c>
       <c r="AJ68" t="s" s="2">
-        <v>142</v>
+        <v>204</v>
       </c>
       <c r="AK68" t="s" s="2">
         <v>79</v>
@@ -10244,13 +10268,13 @@
     </row>
     <row r="69">
       <c r="A69" t="s" s="2">
-        <v>467</v>
+        <v>474</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>466</v>
+        <v>473</v>
       </c>
       <c r="C69" t="s" s="2">
-        <v>468</v>
+        <v>475</v>
       </c>
       <c r="D69" t="s" s="2">
         <v>79</v>
@@ -10272,13 +10296,13 @@
         <v>79</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>469</v>
+        <v>476</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>470</v>
+        <v>477</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>471</v>
+        <v>478</v>
       </c>
       <c r="N69" s="2"/>
       <c r="O69" s="2"/>
@@ -10329,7 +10353,7 @@
         <v>79</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>80</v>
@@ -10341,7 +10365,7 @@
         <v>79</v>
       </c>
       <c r="AJ69" t="s" s="2">
-        <v>142</v>
+        <v>204</v>
       </c>
       <c r="AK69" t="s" s="2">
         <v>79</v>
@@ -10361,13 +10385,13 @@
     </row>
     <row r="70">
       <c r="A70" t="s" s="2">
-        <v>472</v>
+        <v>479</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>466</v>
+        <v>473</v>
       </c>
       <c r="C70" t="s" s="2">
-        <v>473</v>
+        <v>480</v>
       </c>
       <c r="D70" t="s" s="2">
         <v>79</v>
@@ -10389,13 +10413,13 @@
         <v>79</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>474</v>
+        <v>481</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>475</v>
+        <v>482</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>476</v>
+        <v>483</v>
       </c>
       <c r="N70" s="2"/>
       <c r="O70" s="2"/>
@@ -10446,7 +10470,7 @@
         <v>79</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>80</v>
@@ -10458,7 +10482,7 @@
         <v>79</v>
       </c>
       <c r="AJ70" t="s" s="2">
-        <v>142</v>
+        <v>204</v>
       </c>
       <c r="AK70" t="s" s="2">
         <v>79</v>
@@ -10478,10 +10502,10 @@
     </row>
     <row r="71">
       <c r="A71" t="s" s="2">
-        <v>477</v>
+        <v>484</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>477</v>
+        <v>484</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -10504,19 +10528,19 @@
         <v>91</v>
       </c>
       <c r="K71" t="s" s="2">
-        <v>478</v>
+        <v>485</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>479</v>
+        <v>486</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>480</v>
+        <v>487</v>
       </c>
       <c r="N71" t="s" s="2">
-        <v>481</v>
+        <v>488</v>
       </c>
       <c r="O71" t="s" s="2">
-        <v>482</v>
+        <v>489</v>
       </c>
       <c r="P71" t="s" s="2">
         <v>79</v>
@@ -10565,7 +10589,7 @@
         <v>79</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>483</v>
+        <v>490</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>80</v>
@@ -10577,19 +10601,19 @@
         <v>79</v>
       </c>
       <c r="AJ71" t="s" s="2">
-        <v>102</v>
+        <v>214</v>
       </c>
       <c r="AK71" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AL71" t="s" s="2">
-        <v>484</v>
+        <v>491</v>
       </c>
       <c r="AM71" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AN71" t="s" s="2">
-        <v>485</v>
+        <v>492</v>
       </c>
       <c r="AO71" t="s" s="2">
         <v>79</v>
@@ -10597,10 +10621,10 @@
     </row>
     <row r="72">
       <c r="A72" t="s" s="2">
-        <v>486</v>
+        <v>493</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>486</v>
+        <v>493</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -10623,19 +10647,19 @@
         <v>91</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>237</v>
+        <v>240</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>487</v>
+        <v>494</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>488</v>
+        <v>495</v>
       </c>
       <c r="N72" t="s" s="2">
-        <v>489</v>
+        <v>496</v>
       </c>
       <c r="O72" t="s" s="2">
-        <v>490</v>
+        <v>497</v>
       </c>
       <c r="P72" t="s" s="2">
         <v>79</v>
@@ -10684,7 +10708,7 @@
         <v>79</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>491</v>
+        <v>498</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>80</v>
@@ -10696,19 +10720,19 @@
         <v>79</v>
       </c>
       <c r="AJ72" t="s" s="2">
-        <v>102</v>
+        <v>214</v>
       </c>
       <c r="AK72" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AL72" t="s" s="2">
-        <v>492</v>
+        <v>499</v>
       </c>
       <c r="AM72" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AN72" t="s" s="2">
-        <v>493</v>
+        <v>500</v>
       </c>
       <c r="AO72" t="s" s="2">
         <v>79</v>
@@ -10716,10 +10740,10 @@
     </row>
     <row r="73">
       <c r="A73" t="s" s="2">
-        <v>494</v>
+        <v>501</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>494</v>
+        <v>501</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -10742,13 +10766,13 @@
         <v>79</v>
       </c>
       <c r="K73" t="s" s="2">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>495</v>
+        <v>502</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>496</v>
+        <v>503</v>
       </c>
       <c r="N73" s="2"/>
       <c r="O73" s="2"/>
@@ -10779,7 +10803,7 @@
       </c>
       <c r="Y73" s="2"/>
       <c r="Z73" t="s" s="2">
-        <v>497</v>
+        <v>504</v>
       </c>
       <c r="AA73" t="s" s="2">
         <v>79</v>
@@ -10797,7 +10821,7 @@
         <v>79</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>494</v>
+        <v>501</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>80</v>
@@ -10815,13 +10839,13 @@
         <v>79</v>
       </c>
       <c r="AL73" t="s" s="2">
-        <v>498</v>
+        <v>505</v>
       </c>
       <c r="AM73" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AN73" t="s" s="2">
-        <v>499</v>
+        <v>506</v>
       </c>
       <c r="AO73" t="s" s="2">
         <v>79</v>
@@ -10829,10 +10853,10 @@
     </row>
     <row r="74">
       <c r="A74" t="s" s="2">
-        <v>500</v>
+        <v>507</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>500</v>
+        <v>507</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -10944,10 +10968,10 @@
     </row>
     <row r="75">
       <c r="A75" t="s" s="2">
-        <v>501</v>
+        <v>508</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>501</v>
+        <v>508</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -10979,7 +11003,7 @@
         <v>200</v>
       </c>
       <c r="N75" t="s" s="2">
-        <v>174</v>
+        <v>201</v>
       </c>
       <c r="O75" s="2"/>
       <c r="P75" t="s" s="2">
@@ -11020,7 +11044,7 @@
         <v>139</v>
       </c>
       <c r="AC75" t="s" s="2">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="AD75" t="s" s="2">
         <v>79</v>
@@ -11029,7 +11053,7 @@
         <v>140</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>80</v>
@@ -11041,7 +11065,7 @@
         <v>79</v>
       </c>
       <c r="AJ75" t="s" s="2">
-        <v>142</v>
+        <v>204</v>
       </c>
       <c r="AK75" t="s" s="2">
         <v>79</v>
@@ -11061,13 +11085,13 @@
     </row>
     <row r="76">
       <c r="A76" t="s" s="2">
-        <v>502</v>
+        <v>509</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>501</v>
+        <v>508</v>
       </c>
       <c r="C76" t="s" s="2">
-        <v>503</v>
+        <v>510</v>
       </c>
       <c r="D76" t="s" s="2">
         <v>79</v>
@@ -11089,13 +11113,13 @@
         <v>79</v>
       </c>
       <c r="K76" t="s" s="2">
-        <v>504</v>
+        <v>511</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>505</v>
+        <v>512</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>506</v>
+        <v>513</v>
       </c>
       <c r="N76" s="2"/>
       <c r="O76" s="2"/>
@@ -11146,7 +11170,7 @@
         <v>79</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>80</v>
@@ -11158,7 +11182,7 @@
         <v>79</v>
       </c>
       <c r="AJ76" t="s" s="2">
-        <v>142</v>
+        <v>204</v>
       </c>
       <c r="AK76" t="s" s="2">
         <v>79</v>
@@ -11178,10 +11202,10 @@
     </row>
     <row r="77">
       <c r="A77" t="s" s="2">
-        <v>507</v>
+        <v>514</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>507</v>
+        <v>514</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -11204,19 +11228,19 @@
         <v>91</v>
       </c>
       <c r="K77" t="s" s="2">
-        <v>478</v>
+        <v>485</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>479</v>
+        <v>486</v>
       </c>
       <c r="M77" t="s" s="2">
-        <v>480</v>
+        <v>487</v>
       </c>
       <c r="N77" t="s" s="2">
-        <v>481</v>
+        <v>488</v>
       </c>
       <c r="O77" t="s" s="2">
-        <v>482</v>
+        <v>489</v>
       </c>
       <c r="P77" t="s" s="2">
         <v>79</v>
@@ -11265,7 +11289,7 @@
         <v>79</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>483</v>
+        <v>490</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>80</v>
@@ -11277,19 +11301,19 @@
         <v>79</v>
       </c>
       <c r="AJ77" t="s" s="2">
-        <v>102</v>
+        <v>214</v>
       </c>
       <c r="AK77" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AL77" t="s" s="2">
-        <v>484</v>
+        <v>491</v>
       </c>
       <c r="AM77" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AN77" t="s" s="2">
-        <v>485</v>
+        <v>492</v>
       </c>
       <c r="AO77" t="s" s="2">
         <v>79</v>
@@ -11297,10 +11321,10 @@
     </row>
     <row r="78">
       <c r="A78" t="s" s="2">
-        <v>508</v>
+        <v>515</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>508</v>
+        <v>515</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -11323,19 +11347,19 @@
         <v>91</v>
       </c>
       <c r="K78" t="s" s="2">
-        <v>237</v>
+        <v>240</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>487</v>
+        <v>494</v>
       </c>
       <c r="M78" t="s" s="2">
-        <v>488</v>
+        <v>495</v>
       </c>
       <c r="N78" t="s" s="2">
-        <v>489</v>
+        <v>496</v>
       </c>
       <c r="O78" t="s" s="2">
-        <v>490</v>
+        <v>497</v>
       </c>
       <c r="P78" t="s" s="2">
         <v>79</v>
@@ -11384,7 +11408,7 @@
         <v>79</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>491</v>
+        <v>498</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>80</v>
@@ -11396,19 +11420,19 @@
         <v>79</v>
       </c>
       <c r="AJ78" t="s" s="2">
-        <v>102</v>
+        <v>214</v>
       </c>
       <c r="AK78" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AL78" t="s" s="2">
-        <v>492</v>
+        <v>499</v>
       </c>
       <c r="AM78" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AN78" t="s" s="2">
-        <v>493</v>
+        <v>500</v>
       </c>
       <c r="AO78" t="s" s="2">
         <v>79</v>
@@ -11416,10 +11440,10 @@
     </row>
     <row r="79">
       <c r="A79" t="s" s="2">
-        <v>509</v>
+        <v>516</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>509</v>
+        <v>516</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -11442,19 +11466,19 @@
         <v>79</v>
       </c>
       <c r="K79" t="s" s="2">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="L79" t="s" s="2">
-        <v>510</v>
+        <v>517</v>
       </c>
       <c r="M79" t="s" s="2">
-        <v>510</v>
+        <v>517</v>
       </c>
       <c r="N79" t="s" s="2">
-        <v>511</v>
+        <v>518</v>
       </c>
       <c r="O79" t="s" s="2">
-        <v>512</v>
+        <v>519</v>
       </c>
       <c r="P79" t="s" s="2">
         <v>79</v>
@@ -11479,13 +11503,13 @@
         <v>79</v>
       </c>
       <c r="X79" t="s" s="2">
-        <v>305</v>
+        <v>308</v>
       </c>
       <c r="Y79" t="s" s="2">
-        <v>513</v>
+        <v>520</v>
       </c>
       <c r="Z79" t="s" s="2">
-        <v>514</v>
+        <v>521</v>
       </c>
       <c r="AA79" t="s" s="2">
         <v>79</v>
@@ -11503,7 +11527,7 @@
         <v>79</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>509</v>
+        <v>516</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>80</v>
@@ -11521,13 +11545,13 @@
         <v>79</v>
       </c>
       <c r="AL79" t="s" s="2">
-        <v>515</v>
+        <v>522</v>
       </c>
       <c r="AM79" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AN79" t="s" s="2">
-        <v>516</v>
+        <v>523</v>
       </c>
       <c r="AO79" t="s" s="2">
         <v>79</v>
@@ -11535,10 +11559,10 @@
     </row>
     <row r="80">
       <c r="A80" t="s" s="2">
-        <v>517</v>
+        <v>524</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>517</v>
+        <v>524</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -11650,10 +11674,10 @@
     </row>
     <row r="81">
       <c r="A81" t="s" s="2">
-        <v>518</v>
+        <v>525</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>518</v>
+        <v>525</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -11685,7 +11709,7 @@
         <v>200</v>
       </c>
       <c r="N81" t="s" s="2">
-        <v>174</v>
+        <v>201</v>
       </c>
       <c r="O81" s="2"/>
       <c r="P81" t="s" s="2">
@@ -11726,7 +11750,7 @@
         <v>139</v>
       </c>
       <c r="AC81" t="s" s="2">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="AD81" t="s" s="2">
         <v>79</v>
@@ -11735,7 +11759,7 @@
         <v>140</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>80</v>
@@ -11747,7 +11771,7 @@
         <v>79</v>
       </c>
       <c r="AJ81" t="s" s="2">
-        <v>142</v>
+        <v>204</v>
       </c>
       <c r="AK81" t="s" s="2">
         <v>79</v>
@@ -11767,13 +11791,13 @@
     </row>
     <row r="82">
       <c r="A82" t="s" s="2">
-        <v>519</v>
+        <v>526</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>518</v>
+        <v>525</v>
       </c>
       <c r="C82" t="s" s="2">
-        <v>520</v>
+        <v>527</v>
       </c>
       <c r="D82" t="s" s="2">
         <v>79</v>
@@ -11795,13 +11819,13 @@
         <v>79</v>
       </c>
       <c r="K82" t="s" s="2">
-        <v>521</v>
+        <v>528</v>
       </c>
       <c r="L82" t="s" s="2">
-        <v>522</v>
+        <v>529</v>
       </c>
       <c r="M82" t="s" s="2">
-        <v>523</v>
+        <v>530</v>
       </c>
       <c r="N82" s="2"/>
       <c r="O82" s="2"/>
@@ -11852,7 +11876,7 @@
         <v>79</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>80</v>
@@ -11864,7 +11888,7 @@
         <v>79</v>
       </c>
       <c r="AJ82" t="s" s="2">
-        <v>142</v>
+        <v>204</v>
       </c>
       <c r="AK82" t="s" s="2">
         <v>79</v>
@@ -11884,10 +11908,10 @@
     </row>
     <row r="83">
       <c r="A83" t="s" s="2">
-        <v>524</v>
+        <v>531</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>524</v>
+        <v>531</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -11910,19 +11934,19 @@
         <v>91</v>
       </c>
       <c r="K83" t="s" s="2">
-        <v>478</v>
+        <v>485</v>
       </c>
       <c r="L83" t="s" s="2">
-        <v>479</v>
+        <v>486</v>
       </c>
       <c r="M83" t="s" s="2">
-        <v>480</v>
+        <v>487</v>
       </c>
       <c r="N83" t="s" s="2">
-        <v>481</v>
+        <v>488</v>
       </c>
       <c r="O83" t="s" s="2">
-        <v>482</v>
+        <v>489</v>
       </c>
       <c r="P83" t="s" s="2">
         <v>79</v>
@@ -11969,7 +11993,7 @@
         <v>140</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>483</v>
+        <v>490</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>80</v>
@@ -11981,19 +12005,19 @@
         <v>79</v>
       </c>
       <c r="AJ83" t="s" s="2">
-        <v>102</v>
+        <v>214</v>
       </c>
       <c r="AK83" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AL83" t="s" s="2">
-        <v>484</v>
+        <v>491</v>
       </c>
       <c r="AM83" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AN83" t="s" s="2">
-        <v>485</v>
+        <v>492</v>
       </c>
       <c r="AO83" t="s" s="2">
         <v>79</v>
@@ -12001,13 +12025,13 @@
     </row>
     <row r="84">
       <c r="A84" t="s" s="2">
-        <v>525</v>
+        <v>532</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>524</v>
+        <v>531</v>
       </c>
       <c r="C84" t="s" s="2">
-        <v>526</v>
+        <v>533</v>
       </c>
       <c r="D84" t="s" s="2">
         <v>79</v>
@@ -12029,19 +12053,19 @@
         <v>91</v>
       </c>
       <c r="K84" t="s" s="2">
-        <v>478</v>
+        <v>485</v>
       </c>
       <c r="L84" t="s" s="2">
-        <v>527</v>
+        <v>534</v>
       </c>
       <c r="M84" t="s" s="2">
-        <v>528</v>
+        <v>535</v>
       </c>
       <c r="N84" t="s" s="2">
-        <v>529</v>
+        <v>536</v>
       </c>
       <c r="O84" t="s" s="2">
-        <v>530</v>
+        <v>537</v>
       </c>
       <c r="P84" t="s" s="2">
         <v>79</v>
@@ -12070,7 +12094,7 @@
       </c>
       <c r="Y84" s="2"/>
       <c r="Z84" t="s" s="2">
-        <v>531</v>
+        <v>538</v>
       </c>
       <c r="AA84" t="s" s="2">
         <v>79</v>
@@ -12088,7 +12112,7 @@
         <v>79</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>483</v>
+        <v>490</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>80</v>
@@ -12100,19 +12124,19 @@
         <v>79</v>
       </c>
       <c r="AJ84" t="s" s="2">
-        <v>102</v>
+        <v>214</v>
       </c>
       <c r="AK84" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AL84" t="s" s="2">
-        <v>484</v>
+        <v>491</v>
       </c>
       <c r="AM84" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AN84" t="s" s="2">
-        <v>485</v>
+        <v>492</v>
       </c>
       <c r="AO84" t="s" s="2">
         <v>79</v>
@@ -12120,10 +12144,10 @@
     </row>
     <row r="85">
       <c r="A85" t="s" s="2">
-        <v>532</v>
+        <v>539</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>533</v>
+        <v>540</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -12235,10 +12259,10 @@
     </row>
     <row r="86">
       <c r="A86" t="s" s="2">
-        <v>534</v>
+        <v>541</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>535</v>
+        <v>542</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -12270,7 +12294,7 @@
         <v>200</v>
       </c>
       <c r="N86" t="s" s="2">
-        <v>174</v>
+        <v>201</v>
       </c>
       <c r="O86" s="2"/>
       <c r="P86" t="s" s="2">
@@ -12311,7 +12335,7 @@
         <v>139</v>
       </c>
       <c r="AC86" t="s" s="2">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="AD86" t="s" s="2">
         <v>79</v>
@@ -12320,7 +12344,7 @@
         <v>140</v>
       </c>
       <c r="AF86" t="s" s="2">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="AG86" t="s" s="2">
         <v>80</v>
@@ -12332,7 +12356,7 @@
         <v>79</v>
       </c>
       <c r="AJ86" t="s" s="2">
-        <v>142</v>
+        <v>204</v>
       </c>
       <c r="AK86" t="s" s="2">
         <v>79</v>
@@ -12352,10 +12376,10 @@
     </row>
     <row r="87">
       <c r="A87" t="s" s="2">
-        <v>536</v>
+        <v>543</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>537</v>
+        <v>544</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
@@ -12381,23 +12405,23 @@
         <v>104</v>
       </c>
       <c r="L87" t="s" s="2">
-        <v>538</v>
+        <v>545</v>
       </c>
       <c r="M87" t="s" s="2">
-        <v>539</v>
+        <v>546</v>
       </c>
       <c r="N87" t="s" s="2">
-        <v>540</v>
+        <v>547</v>
       </c>
       <c r="O87" t="s" s="2">
-        <v>541</v>
+        <v>548</v>
       </c>
       <c r="P87" t="s" s="2">
         <v>79</v>
       </c>
       <c r="Q87" s="2"/>
       <c r="R87" t="s" s="2">
-        <v>542</v>
+        <v>549</v>
       </c>
       <c r="S87" t="s" s="2">
         <v>79</v>
@@ -12439,7 +12463,7 @@
         <v>79</v>
       </c>
       <c r="AF87" t="s" s="2">
-        <v>543</v>
+        <v>550</v>
       </c>
       <c r="AG87" t="s" s="2">
         <v>80</v>
@@ -12451,19 +12475,19 @@
         <v>79</v>
       </c>
       <c r="AJ87" t="s" s="2">
-        <v>102</v>
+        <v>214</v>
       </c>
       <c r="AK87" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AL87" t="s" s="2">
-        <v>544</v>
+        <v>551</v>
       </c>
       <c r="AM87" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AN87" t="s" s="2">
-        <v>545</v>
+        <v>552</v>
       </c>
       <c r="AO87" t="s" s="2">
         <v>79</v>
@@ -12471,10 +12495,10 @@
     </row>
     <row r="88">
       <c r="A88" t="s" s="2">
-        <v>546</v>
+        <v>553</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>547</v>
+        <v>554</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
@@ -12497,16 +12521,16 @@
         <v>91</v>
       </c>
       <c r="K88" t="s" s="2">
-        <v>237</v>
+        <v>240</v>
       </c>
       <c r="L88" t="s" s="2">
-        <v>548</v>
+        <v>555</v>
       </c>
       <c r="M88" t="s" s="2">
-        <v>549</v>
+        <v>556</v>
       </c>
       <c r="N88" t="s" s="2">
-        <v>550</v>
+        <v>557</v>
       </c>
       <c r="O88" s="2"/>
       <c r="P88" t="s" s="2">
@@ -12556,7 +12580,7 @@
         <v>79</v>
       </c>
       <c r="AF88" t="s" s="2">
-        <v>551</v>
+        <v>558</v>
       </c>
       <c r="AG88" t="s" s="2">
         <v>80</v>
@@ -12568,19 +12592,19 @@
         <v>79</v>
       </c>
       <c r="AJ88" t="s" s="2">
-        <v>102</v>
+        <v>214</v>
       </c>
       <c r="AK88" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AL88" t="s" s="2">
-        <v>552</v>
+        <v>559</v>
       </c>
       <c r="AM88" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AN88" t="s" s="2">
-        <v>553</v>
+        <v>560</v>
       </c>
       <c r="AO88" t="s" s="2">
         <v>79</v>
@@ -12588,10 +12612,10 @@
     </row>
     <row r="89">
       <c r="A89" t="s" s="2">
-        <v>554</v>
+        <v>561</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>555</v>
+        <v>562</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
@@ -12617,14 +12641,14 @@
         <v>110</v>
       </c>
       <c r="L89" t="s" s="2">
-        <v>556</v>
+        <v>563</v>
       </c>
       <c r="M89" t="s" s="2">
-        <v>557</v>
+        <v>564</v>
       </c>
       <c r="N89" s="2"/>
       <c r="O89" t="s" s="2">
-        <v>558</v>
+        <v>565</v>
       </c>
       <c r="P89" t="s" s="2">
         <v>79</v>
@@ -12673,7 +12697,7 @@
         <v>79</v>
       </c>
       <c r="AF89" t="s" s="2">
-        <v>559</v>
+        <v>566</v>
       </c>
       <c r="AG89" t="s" s="2">
         <v>80</v>
@@ -12685,19 +12709,19 @@
         <v>79</v>
       </c>
       <c r="AJ89" t="s" s="2">
-        <v>102</v>
+        <v>214</v>
       </c>
       <c r="AK89" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AL89" t="s" s="2">
-        <v>560</v>
+        <v>567</v>
       </c>
       <c r="AM89" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AN89" t="s" s="2">
-        <v>561</v>
+        <v>568</v>
       </c>
       <c r="AO89" t="s" s="2">
         <v>79</v>
@@ -12705,10 +12729,10 @@
     </row>
     <row r="90">
       <c r="A90" t="s" s="2">
-        <v>562</v>
+        <v>569</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>563</v>
+        <v>570</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
@@ -12731,17 +12755,17 @@
         <v>91</v>
       </c>
       <c r="K90" t="s" s="2">
-        <v>237</v>
+        <v>240</v>
       </c>
       <c r="L90" t="s" s="2">
-        <v>564</v>
+        <v>571</v>
       </c>
       <c r="M90" t="s" s="2">
-        <v>565</v>
+        <v>572</v>
       </c>
       <c r="N90" s="2"/>
       <c r="O90" t="s" s="2">
-        <v>566</v>
+        <v>573</v>
       </c>
       <c r="P90" t="s" s="2">
         <v>79</v>
@@ -12790,7 +12814,7 @@
         <v>79</v>
       </c>
       <c r="AF90" t="s" s="2">
-        <v>567</v>
+        <v>574</v>
       </c>
       <c r="AG90" t="s" s="2">
         <v>80</v>
@@ -12802,19 +12826,19 @@
         <v>79</v>
       </c>
       <c r="AJ90" t="s" s="2">
-        <v>102</v>
+        <v>214</v>
       </c>
       <c r="AK90" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AL90" t="s" s="2">
-        <v>568</v>
+        <v>575</v>
       </c>
       <c r="AM90" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AN90" t="s" s="2">
-        <v>569</v>
+        <v>576</v>
       </c>
       <c r="AO90" t="s" s="2">
         <v>79</v>
@@ -12822,10 +12846,10 @@
     </row>
     <row r="91">
       <c r="A91" t="s" s="2">
-        <v>570</v>
+        <v>577</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>571</v>
+        <v>578</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
@@ -12848,19 +12872,19 @@
         <v>91</v>
       </c>
       <c r="K91" t="s" s="2">
-        <v>572</v>
+        <v>579</v>
       </c>
       <c r="L91" t="s" s="2">
-        <v>573</v>
+        <v>580</v>
       </c>
       <c r="M91" t="s" s="2">
-        <v>574</v>
+        <v>581</v>
       </c>
       <c r="N91" t="s" s="2">
-        <v>575</v>
+        <v>582</v>
       </c>
       <c r="O91" t="s" s="2">
-        <v>576</v>
+        <v>583</v>
       </c>
       <c r="P91" t="s" s="2">
         <v>79</v>
@@ -12909,7 +12933,7 @@
         <v>79</v>
       </c>
       <c r="AF91" t="s" s="2">
-        <v>577</v>
+        <v>584</v>
       </c>
       <c r="AG91" t="s" s="2">
         <v>80</v>
@@ -12921,19 +12945,19 @@
         <v>79</v>
       </c>
       <c r="AJ91" t="s" s="2">
-        <v>102</v>
+        <v>214</v>
       </c>
       <c r="AK91" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AL91" t="s" s="2">
-        <v>578</v>
+        <v>585</v>
       </c>
       <c r="AM91" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AN91" t="s" s="2">
-        <v>579</v>
+        <v>586</v>
       </c>
       <c r="AO91" t="s" s="2">
         <v>79</v>
@@ -12941,13 +12965,13 @@
     </row>
     <row r="92">
       <c r="A92" t="s" s="2">
-        <v>580</v>
+        <v>587</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>524</v>
+        <v>531</v>
       </c>
       <c r="C92" t="s" s="2">
-        <v>581</v>
+        <v>588</v>
       </c>
       <c r="D92" t="s" s="2">
         <v>79</v>
@@ -12969,19 +12993,19 @@
         <v>91</v>
       </c>
       <c r="K92" t="s" s="2">
-        <v>478</v>
+        <v>485</v>
       </c>
       <c r="L92" t="s" s="2">
-        <v>582</v>
+        <v>589</v>
       </c>
       <c r="M92" t="s" s="2">
-        <v>583</v>
+        <v>590</v>
       </c>
       <c r="N92" t="s" s="2">
-        <v>529</v>
+        <v>536</v>
       </c>
       <c r="O92" t="s" s="2">
-        <v>530</v>
+        <v>537</v>
       </c>
       <c r="P92" t="s" s="2">
         <v>79</v>
@@ -13010,7 +13034,7 @@
       </c>
       <c r="Y92" s="2"/>
       <c r="Z92" t="s" s="2">
-        <v>584</v>
+        <v>591</v>
       </c>
       <c r="AA92" t="s" s="2">
         <v>79</v>
@@ -13028,7 +13052,7 @@
         <v>79</v>
       </c>
       <c r="AF92" t="s" s="2">
-        <v>483</v>
+        <v>490</v>
       </c>
       <c r="AG92" t="s" s="2">
         <v>80</v>
@@ -13040,19 +13064,19 @@
         <v>79</v>
       </c>
       <c r="AJ92" t="s" s="2">
-        <v>102</v>
+        <v>214</v>
       </c>
       <c r="AK92" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AL92" t="s" s="2">
-        <v>484</v>
+        <v>491</v>
       </c>
       <c r="AM92" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AN92" t="s" s="2">
-        <v>485</v>
+        <v>492</v>
       </c>
       <c r="AO92" t="s" s="2">
         <v>79</v>
@@ -13060,10 +13084,10 @@
     </row>
     <row r="93">
       <c r="A93" t="s" s="2">
-        <v>585</v>
+        <v>592</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>533</v>
+        <v>540</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
@@ -13175,10 +13199,10 @@
     </row>
     <row r="94">
       <c r="A94" t="s" s="2">
-        <v>586</v>
+        <v>593</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>535</v>
+        <v>542</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
@@ -13210,7 +13234,7 @@
         <v>200</v>
       </c>
       <c r="N94" t="s" s="2">
-        <v>174</v>
+        <v>201</v>
       </c>
       <c r="O94" s="2"/>
       <c r="P94" t="s" s="2">
@@ -13251,7 +13275,7 @@
         <v>139</v>
       </c>
       <c r="AC94" t="s" s="2">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="AD94" t="s" s="2">
         <v>79</v>
@@ -13260,7 +13284,7 @@
         <v>140</v>
       </c>
       <c r="AF94" t="s" s="2">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="AG94" t="s" s="2">
         <v>80</v>
@@ -13272,7 +13296,7 @@
         <v>79</v>
       </c>
       <c r="AJ94" t="s" s="2">
-        <v>142</v>
+        <v>204</v>
       </c>
       <c r="AK94" t="s" s="2">
         <v>79</v>
@@ -13292,10 +13316,10 @@
     </row>
     <row r="95">
       <c r="A95" t="s" s="2">
-        <v>587</v>
+        <v>594</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>537</v>
+        <v>544</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
@@ -13321,23 +13345,23 @@
         <v>104</v>
       </c>
       <c r="L95" t="s" s="2">
-        <v>538</v>
+        <v>545</v>
       </c>
       <c r="M95" t="s" s="2">
-        <v>539</v>
+        <v>546</v>
       </c>
       <c r="N95" t="s" s="2">
-        <v>540</v>
+        <v>547</v>
       </c>
       <c r="O95" t="s" s="2">
-        <v>541</v>
+        <v>548</v>
       </c>
       <c r="P95" t="s" s="2">
         <v>79</v>
       </c>
       <c r="Q95" s="2"/>
       <c r="R95" t="s" s="2">
-        <v>588</v>
+        <v>595</v>
       </c>
       <c r="S95" t="s" s="2">
         <v>79</v>
@@ -13379,7 +13403,7 @@
         <v>79</v>
       </c>
       <c r="AF95" t="s" s="2">
-        <v>543</v>
+        <v>550</v>
       </c>
       <c r="AG95" t="s" s="2">
         <v>80</v>
@@ -13391,19 +13415,19 @@
         <v>79</v>
       </c>
       <c r="AJ95" t="s" s="2">
-        <v>102</v>
+        <v>214</v>
       </c>
       <c r="AK95" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AL95" t="s" s="2">
-        <v>544</v>
+        <v>551</v>
       </c>
       <c r="AM95" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AN95" t="s" s="2">
-        <v>545</v>
+        <v>552</v>
       </c>
       <c r="AO95" t="s" s="2">
         <v>79</v>
@@ -13411,10 +13435,10 @@
     </row>
     <row r="96">
       <c r="A96" t="s" s="2">
-        <v>589</v>
+        <v>596</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>547</v>
+        <v>554</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
@@ -13437,16 +13461,16 @@
         <v>91</v>
       </c>
       <c r="K96" t="s" s="2">
-        <v>237</v>
+        <v>240</v>
       </c>
       <c r="L96" t="s" s="2">
-        <v>548</v>
+        <v>555</v>
       </c>
       <c r="M96" t="s" s="2">
-        <v>549</v>
+        <v>556</v>
       </c>
       <c r="N96" t="s" s="2">
-        <v>550</v>
+        <v>557</v>
       </c>
       <c r="O96" s="2"/>
       <c r="P96" t="s" s="2">
@@ -13496,7 +13520,7 @@
         <v>79</v>
       </c>
       <c r="AF96" t="s" s="2">
-        <v>551</v>
+        <v>558</v>
       </c>
       <c r="AG96" t="s" s="2">
         <v>80</v>
@@ -13508,19 +13532,19 @@
         <v>79</v>
       </c>
       <c r="AJ96" t="s" s="2">
-        <v>102</v>
+        <v>214</v>
       </c>
       <c r="AK96" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AL96" t="s" s="2">
-        <v>552</v>
+        <v>559</v>
       </c>
       <c r="AM96" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AN96" t="s" s="2">
-        <v>553</v>
+        <v>560</v>
       </c>
       <c r="AO96" t="s" s="2">
         <v>79</v>
@@ -13528,10 +13552,10 @@
     </row>
     <row r="97">
       <c r="A97" t="s" s="2">
-        <v>590</v>
+        <v>597</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>555</v>
+        <v>562</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
@@ -13557,14 +13581,14 @@
         <v>110</v>
       </c>
       <c r="L97" t="s" s="2">
-        <v>556</v>
+        <v>563</v>
       </c>
       <c r="M97" t="s" s="2">
-        <v>557</v>
+        <v>564</v>
       </c>
       <c r="N97" s="2"/>
       <c r="O97" t="s" s="2">
-        <v>558</v>
+        <v>565</v>
       </c>
       <c r="P97" t="s" s="2">
         <v>79</v>
@@ -13613,7 +13637,7 @@
         <v>79</v>
       </c>
       <c r="AF97" t="s" s="2">
-        <v>559</v>
+        <v>566</v>
       </c>
       <c r="AG97" t="s" s="2">
         <v>80</v>
@@ -13625,19 +13649,19 @@
         <v>79</v>
       </c>
       <c r="AJ97" t="s" s="2">
-        <v>102</v>
+        <v>214</v>
       </c>
       <c r="AK97" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AL97" t="s" s="2">
-        <v>560</v>
+        <v>567</v>
       </c>
       <c r="AM97" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AN97" t="s" s="2">
-        <v>561</v>
+        <v>568</v>
       </c>
       <c r="AO97" t="s" s="2">
         <v>79</v>
@@ -13645,10 +13669,10 @@
     </row>
     <row r="98">
       <c r="A98" t="s" s="2">
-        <v>591</v>
+        <v>598</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>563</v>
+        <v>570</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
@@ -13671,17 +13695,17 @@
         <v>91</v>
       </c>
       <c r="K98" t="s" s="2">
-        <v>237</v>
+        <v>240</v>
       </c>
       <c r="L98" t="s" s="2">
-        <v>564</v>
+        <v>571</v>
       </c>
       <c r="M98" t="s" s="2">
-        <v>565</v>
+        <v>572</v>
       </c>
       <c r="N98" s="2"/>
       <c r="O98" t="s" s="2">
-        <v>566</v>
+        <v>573</v>
       </c>
       <c r="P98" t="s" s="2">
         <v>79</v>
@@ -13730,7 +13754,7 @@
         <v>79</v>
       </c>
       <c r="AF98" t="s" s="2">
-        <v>567</v>
+        <v>574</v>
       </c>
       <c r="AG98" t="s" s="2">
         <v>80</v>
@@ -13742,19 +13766,19 @@
         <v>79</v>
       </c>
       <c r="AJ98" t="s" s="2">
-        <v>102</v>
+        <v>214</v>
       </c>
       <c r="AK98" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AL98" t="s" s="2">
-        <v>568</v>
+        <v>575</v>
       </c>
       <c r="AM98" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AN98" t="s" s="2">
-        <v>569</v>
+        <v>576</v>
       </c>
       <c r="AO98" t="s" s="2">
         <v>79</v>
@@ -13762,10 +13786,10 @@
     </row>
     <row r="99">
       <c r="A99" t="s" s="2">
-        <v>592</v>
+        <v>599</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>571</v>
+        <v>578</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" t="s" s="2">
@@ -13788,19 +13812,19 @@
         <v>91</v>
       </c>
       <c r="K99" t="s" s="2">
-        <v>572</v>
+        <v>579</v>
       </c>
       <c r="L99" t="s" s="2">
-        <v>573</v>
+        <v>580</v>
       </c>
       <c r="M99" t="s" s="2">
-        <v>574</v>
+        <v>581</v>
       </c>
       <c r="N99" t="s" s="2">
-        <v>575</v>
+        <v>582</v>
       </c>
       <c r="O99" t="s" s="2">
-        <v>576</v>
+        <v>583</v>
       </c>
       <c r="P99" t="s" s="2">
         <v>79</v>
@@ -13849,7 +13873,7 @@
         <v>79</v>
       </c>
       <c r="AF99" t="s" s="2">
-        <v>577</v>
+        <v>584</v>
       </c>
       <c r="AG99" t="s" s="2">
         <v>80</v>
@@ -13861,19 +13885,19 @@
         <v>79</v>
       </c>
       <c r="AJ99" t="s" s="2">
-        <v>102</v>
+        <v>214</v>
       </c>
       <c r="AK99" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AL99" t="s" s="2">
-        <v>578</v>
+        <v>585</v>
       </c>
       <c r="AM99" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AN99" t="s" s="2">
-        <v>579</v>
+        <v>586</v>
       </c>
       <c r="AO99" t="s" s="2">
         <v>79</v>
@@ -13881,10 +13905,10 @@
     </row>
     <row r="100">
       <c r="A100" t="s" s="2">
-        <v>593</v>
+        <v>600</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>593</v>
+        <v>600</v>
       </c>
       <c r="C100" s="2"/>
       <c r="D100" t="s" s="2">
@@ -13907,19 +13931,19 @@
         <v>91</v>
       </c>
       <c r="K100" t="s" s="2">
-        <v>237</v>
+        <v>240</v>
       </c>
       <c r="L100" t="s" s="2">
-        <v>594</v>
+        <v>601</v>
       </c>
       <c r="M100" t="s" s="2">
-        <v>595</v>
+        <v>602</v>
       </c>
       <c r="N100" t="s" s="2">
-        <v>596</v>
+        <v>603</v>
       </c>
       <c r="O100" t="s" s="2">
-        <v>597</v>
+        <v>604</v>
       </c>
       <c r="P100" t="s" s="2">
         <v>79</v>
@@ -13968,7 +13992,7 @@
         <v>79</v>
       </c>
       <c r="AF100" t="s" s="2">
-        <v>491</v>
+        <v>498</v>
       </c>
       <c r="AG100" t="s" s="2">
         <v>80</v>
@@ -13980,19 +14004,19 @@
         <v>79</v>
       </c>
       <c r="AJ100" t="s" s="2">
-        <v>102</v>
+        <v>214</v>
       </c>
       <c r="AK100" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AL100" t="s" s="2">
-        <v>492</v>
+        <v>499</v>
       </c>
       <c r="AM100" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AN100" t="s" s="2">
-        <v>493</v>
+        <v>500</v>
       </c>
       <c r="AO100" t="s" s="2">
         <v>79</v>
@@ -14000,10 +14024,10 @@
     </row>
     <row r="101">
       <c r="A101" t="s" s="2">
-        <v>598</v>
+        <v>605</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>598</v>
+        <v>605</v>
       </c>
       <c r="C101" s="2"/>
       <c r="D101" t="s" s="2">
@@ -14026,16 +14050,16 @@
         <v>79</v>
       </c>
       <c r="K101" t="s" s="2">
-        <v>599</v>
+        <v>606</v>
       </c>
       <c r="L101" t="s" s="2">
-        <v>600</v>
+        <v>607</v>
       </c>
       <c r="M101" t="s" s="2">
-        <v>601</v>
+        <v>608</v>
       </c>
       <c r="N101" t="s" s="2">
-        <v>602</v>
+        <v>609</v>
       </c>
       <c r="O101" s="2"/>
       <c r="P101" t="s" s="2">
@@ -14085,7 +14109,7 @@
         <v>79</v>
       </c>
       <c r="AF101" t="s" s="2">
-        <v>598</v>
+        <v>605</v>
       </c>
       <c r="AG101" t="s" s="2">
         <v>80</v>
@@ -14103,13 +14127,13 @@
         <v>79</v>
       </c>
       <c r="AL101" t="s" s="2">
-        <v>603</v>
+        <v>610</v>
       </c>
       <c r="AM101" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AN101" t="s" s="2">
-        <v>604</v>
+        <v>611</v>
       </c>
       <c r="AO101" t="s" s="2">
         <v>79</v>
@@ -14117,10 +14141,10 @@
     </row>
     <row r="102">
       <c r="A102" t="s" s="2">
-        <v>605</v>
+        <v>612</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>605</v>
+        <v>612</v>
       </c>
       <c r="C102" s="2"/>
       <c r="D102" t="s" s="2">
@@ -14143,16 +14167,16 @@
         <v>79</v>
       </c>
       <c r="K102" t="s" s="2">
-        <v>606</v>
+        <v>613</v>
       </c>
       <c r="L102" t="s" s="2">
-        <v>607</v>
+        <v>614</v>
       </c>
       <c r="M102" t="s" s="2">
-        <v>608</v>
+        <v>615</v>
       </c>
       <c r="N102" t="s" s="2">
-        <v>609</v>
+        <v>616</v>
       </c>
       <c r="O102" s="2"/>
       <c r="P102" t="s" s="2">
@@ -14190,17 +14214,17 @@
         <v>79</v>
       </c>
       <c r="AB102" t="s" s="2">
-        <v>610</v>
+        <v>617</v>
       </c>
       <c r="AC102" s="2"/>
       <c r="AD102" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AE102" t="s" s="2">
-        <v>611</v>
+        <v>618</v>
       </c>
       <c r="AF102" t="s" s="2">
-        <v>605</v>
+        <v>612</v>
       </c>
       <c r="AG102" t="s" s="2">
         <v>80</v>
@@ -14218,13 +14242,13 @@
         <v>79</v>
       </c>
       <c r="AL102" t="s" s="2">
-        <v>612</v>
+        <v>619</v>
       </c>
       <c r="AM102" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AN102" t="s" s="2">
-        <v>613</v>
+        <v>620</v>
       </c>
       <c r="AO102" t="s" s="2">
         <v>79</v>
@@ -14232,13 +14256,13 @@
     </row>
     <row r="103">
       <c r="A103" t="s" s="2">
-        <v>614</v>
+        <v>621</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>605</v>
+        <v>612</v>
       </c>
       <c r="C103" t="s" s="2">
-        <v>615</v>
+        <v>622</v>
       </c>
       <c r="D103" t="s" s="2">
         <v>79</v>
@@ -14260,16 +14284,16 @@
         <v>79</v>
       </c>
       <c r="K103" t="s" s="2">
-        <v>616</v>
+        <v>623</v>
       </c>
       <c r="L103" t="s" s="2">
-        <v>617</v>
+        <v>624</v>
       </c>
       <c r="M103" t="s" s="2">
-        <v>618</v>
+        <v>625</v>
       </c>
       <c r="N103" t="s" s="2">
-        <v>619</v>
+        <v>626</v>
       </c>
       <c r="O103" s="2"/>
       <c r="P103" t="s" s="2">
@@ -14319,7 +14343,7 @@
         <v>79</v>
       </c>
       <c r="AF103" t="s" s="2">
-        <v>605</v>
+        <v>612</v>
       </c>
       <c r="AG103" t="s" s="2">
         <v>80</v>
@@ -14337,13 +14361,13 @@
         <v>79</v>
       </c>
       <c r="AL103" t="s" s="2">
-        <v>612</v>
+        <v>619</v>
       </c>
       <c r="AM103" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AN103" t="s" s="2">
-        <v>613</v>
+        <v>620</v>
       </c>
       <c r="AO103" t="s" s="2">
         <v>79</v>
@@ -14351,13 +14375,13 @@
     </row>
     <row r="104">
       <c r="A104" t="s" s="2">
-        <v>620</v>
+        <v>627</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>605</v>
+        <v>612</v>
       </c>
       <c r="C104" t="s" s="2">
-        <v>621</v>
+        <v>628</v>
       </c>
       <c r="D104" t="s" s="2">
         <v>79</v>
@@ -14379,16 +14403,16 @@
         <v>79</v>
       </c>
       <c r="K104" t="s" s="2">
-        <v>622</v>
+        <v>629</v>
       </c>
       <c r="L104" t="s" s="2">
-        <v>623</v>
+        <v>630</v>
       </c>
       <c r="M104" t="s" s="2">
-        <v>623</v>
+        <v>630</v>
       </c>
       <c r="N104" t="s" s="2">
-        <v>619</v>
+        <v>626</v>
       </c>
       <c r="O104" s="2"/>
       <c r="P104" t="s" s="2">
@@ -14438,7 +14462,7 @@
         <v>79</v>
       </c>
       <c r="AF104" t="s" s="2">
-        <v>605</v>
+        <v>612</v>
       </c>
       <c r="AG104" t="s" s="2">
         <v>80</v>
@@ -14456,13 +14480,13 @@
         <v>79</v>
       </c>
       <c r="AL104" t="s" s="2">
-        <v>612</v>
+        <v>619</v>
       </c>
       <c r="AM104" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AN104" t="s" s="2">
-        <v>613</v>
+        <v>620</v>
       </c>
       <c r="AO104" t="s" s="2">
         <v>79</v>
@@ -14470,10 +14494,10 @@
     </row>
     <row r="105">
       <c r="A105" t="s" s="2">
-        <v>624</v>
+        <v>631</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>624</v>
+        <v>631</v>
       </c>
       <c r="C105" s="2"/>
       <c r="D105" t="s" s="2">
@@ -14496,16 +14520,16 @@
         <v>79</v>
       </c>
       <c r="K105" t="s" s="2">
-        <v>625</v>
+        <v>632</v>
       </c>
       <c r="L105" t="s" s="2">
-        <v>626</v>
+        <v>633</v>
       </c>
       <c r="M105" t="s" s="2">
-        <v>627</v>
+        <v>634</v>
       </c>
       <c r="N105" t="s" s="2">
-        <v>628</v>
+        <v>635</v>
       </c>
       <c r="O105" s="2"/>
       <c r="P105" t="s" s="2">
@@ -14555,7 +14579,7 @@
         <v>79</v>
       </c>
       <c r="AF105" t="s" s="2">
-        <v>624</v>
+        <v>631</v>
       </c>
       <c r="AG105" t="s" s="2">
         <v>80</v>
@@ -14573,7 +14597,7 @@
         <v>79</v>
       </c>
       <c r="AL105" t="s" s="2">
-        <v>629</v>
+        <v>636</v>
       </c>
       <c r="AM105" t="s" s="2">
         <v>79</v>
